--- a/Översikt PAJALA.xlsx
+++ b/Översikt PAJALA.xlsx
@@ -601,7 +601,7 @@
         <v>45880</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>44874</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>45749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45345</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>45502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44503</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>45407</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45845</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>46197</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>44608</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>45306</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>46171</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>44588</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>44608</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>45981</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>45405</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>46258</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>46260</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>44487</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>44608</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44874</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44608</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44893</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>45964</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>46211</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>45841</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>45671</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>44943</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>44503</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>45902</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>46029</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>46182</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>46182</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>46254</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>46212</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>45469</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>45499</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>45959</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>46052</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>45530</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>45957</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44760</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>45946</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>44755</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>44513</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>45392</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>45643</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>44608</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>44945</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>45476</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>45973</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>44895</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>45530</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>45196</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>46253</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>45769</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>46237</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45150</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>44771</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>45163</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>45897</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>44930</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>45902</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>45755</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>46034</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>46178</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>45215</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>44964</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>46182</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>46196</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>46107</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>46204</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>46178</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>46258</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>46216</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>46273</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>46274</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>46275</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>46237</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>44496</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44608</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>45356</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>45575</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>45585</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>45894</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>45894</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45254</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>45611</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>45497</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>45938</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>46153</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>45722</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>45585</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>46035</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>46188</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>44854</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>44854</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>46189</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>46189</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>45121</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>46125</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>46128</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>46204</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>46251</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>46196</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>45216</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>46227</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>46276</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>45791</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>45820</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>45832</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45838</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>45875</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>44579</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>45394</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44691</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44755</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>44691</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>44532</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>44476</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>44755</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>44755</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>44755</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>44602</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>44523</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>44691</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>44691</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>44691</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>44496</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>44700</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>44756</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>44622</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>44879</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>44837</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>44884</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>44627</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>44642</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>44875</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>44691</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>44629</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>44592</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>44634</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44663</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>44869</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>44627</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>44873</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>44873</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>44462</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>44518</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>44834</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>44663</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>44552</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>44796</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44550</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>44749</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>44663</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>44464</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>44521</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>44860</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>44862</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>44627</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>44691</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>45467</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>44804</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>45613</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>44874</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>45275</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>45698</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         <v>45611</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>45454</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         <v>45238</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>45238</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>44504</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         <v>44608</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>45523</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45611</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45575</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>45217</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>44960</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>44960</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>45477</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>45054</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         <v>45540</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>44522</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18985,7 +18985,7 @@
         <v>45665</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>45475</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19131,7 +19131,7 @@
         <v>45573</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>44874</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>44756</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>45566</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>44892</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>44517</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>44910</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>45486</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>45601</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>45169</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>45592</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>45201</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20022,7 +20022,7 @@
         <v>45187</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20095,7 +20095,7 @@
         <v>45455</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>45611</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>45678</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>45667</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>45469</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20465,7 +20465,7 @@
         <v>45562</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>44477</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>45227</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>45334</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>45180</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
         <v>45477</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
         <v>45505</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>45154</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>45334</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>45227</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>45583</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44884</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>45447</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>45631</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>45764</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44960</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>44894</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         <v>44916</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>45387</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>44547</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45482</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>45660</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45660</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45481</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>44568</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>45215</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45557</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>45707</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>45579</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>45579</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>45177</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44973</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>45474</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45477</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44467</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>46136</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>45491</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>45316</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>45454</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>45434</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>45895</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>45894</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>45599</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>45603</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23722,7 +23722,7 @@
         <v>46134</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>45897</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>46136</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>45899</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45898</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>45884</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>45898</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>45902</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45902</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>45905</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24482,7 +24482,7 @@
         <v>45906</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>45909</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>45910</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>45297</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>45909</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45914</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>45152</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>45918</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25071,7 +25071,7 @@
         <v>44968</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>44518</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>45919</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>45919</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45918</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>44578</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>45923</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>45923</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>45498</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>45922</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25816,7 +25816,7 @@
         <v>45406</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>45919</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>45012</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>45925</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>44892</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>45925</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>45925</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>45925</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26400,7 +26400,7 @@
         <v>45862</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>44459</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>45926</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45356</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>44861</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>45624</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>45177</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>45930</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>45623</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>45616</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>45936</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>45934</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>45936</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>46147</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>45936</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27515,7 +27515,7 @@
         <v>45936</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>45118</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27666,7 +27666,7 @@
         <v>45936</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>45586</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27812,7 +27812,7 @@
         <v>45586</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>46146</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>46146</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28031,7 +28031,7 @@
         <v>45938</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28104,7 +28104,7 @@
         <v>45938</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         <v>45938</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>45580</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>45058</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>45671</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>45938</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>45938</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>45870</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>45939</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>45943</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45560</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45943</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>44790</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>45944</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29136,7 +29136,7 @@
         <v>45427</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>45630</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>45218</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29355,7 +29355,7 @@
         <v>45951</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>45944</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>45136</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29574,7 +29574,7 @@
         <v>44988</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>45592</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>45592</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>45682</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29866,7 +29866,7 @@
         <v>45265</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>45247</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>45965</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>45964</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>45964</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44778</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>44755</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>44834</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>44755</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>46155</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>45968</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>45970</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45968</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45971</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>45968</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>45972</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>45972</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>45972</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>45972</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>45972</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>45972</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>45972</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>45972</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>45972</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>45972</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>45972</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45972</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>45974</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>45975</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>45443</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32071,7 +32071,7 @@
         <v>45981</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32144,7 +32144,7 @@
         <v>45981</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>45981</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32290,7 +32290,7 @@
         <v>45980</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>45314</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>45589</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32514,7 +32514,7 @@
         <v>44968</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45988</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>45031</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>45270</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>44968</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>46162</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32952,7 +32952,7 @@
         <v>45631</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>46162</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>46162</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>45740</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>45995</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33322,7 +33322,7 @@
         <v>46161</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>45960</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33468,7 +33468,7 @@
         <v>45878</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>45210</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44837</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33687,7 +33687,7 @@
         <v>45972</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33760,7 +33760,7 @@
         <v>44552</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33838,7 +33838,7 @@
         <v>46002</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33911,7 +33911,7 @@
         <v>44908</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>46002</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34062,7 +34062,7 @@
         <v>46002</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>45440</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34213,7 +34213,7 @@
         <v>45736</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>46002</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>45960</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34437,7 +34437,7 @@
         <v>45970</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34510,7 +34510,7 @@
         <v>45443</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34583,7 +34583,7 @@
         <v>46002</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34656,7 +34656,7 @@
         <v>46002</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34734,7 +34734,7 @@
         <v>46006</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>46006</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34880,7 +34880,7 @@
         <v>44889</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>46006</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>45597</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35104,7 +35104,7 @@
         <v>45062</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35177,7 +35177,7 @@
         <v>45611</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>45523</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>45064</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>44841</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35469,7 +35469,7 @@
         <v>46020</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35542,7 +35542,7 @@
         <v>46021</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>46021</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>45271</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>46020</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35834,7 +35834,7 @@
         <v>45630</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35907,7 +35907,7 @@
         <v>46029</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35985,7 +35985,7 @@
         <v>46029</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36063,7 +36063,7 @@
         <v>46029</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36136,7 +36136,7 @@
         <v>46029</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>46029</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>45370</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36365,7 +36365,7 @@
         <v>46029</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>46031</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36516,7 +36516,7 @@
         <v>46031</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>46030</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36662,7 +36662,7 @@
         <v>46171</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>46170</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36813,7 +36813,7 @@
         <v>46034</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36886,7 +36886,7 @@
         <v>45463</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36964,7 +36964,7 @@
         <v>46173</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37037,7 +37037,7 @@
         <v>46038</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>45391</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>46174</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37261,7 +37261,7 @@
         <v>46173</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
         <v>46049</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37412,7 +37412,7 @@
         <v>46048</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37485,7 +37485,7 @@
         <v>44970</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         <v>44860</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37631,7 +37631,7 @@
         <v>46049</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>45131</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37782,7 +37782,7 @@
         <v>46181</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>46052</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>46181</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38001,7 +38001,7 @@
         <v>46181</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>45970</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38147,7 +38147,7 @@
         <v>46177</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45558</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>44958</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38366,7 +38366,7 @@
         <v>46059</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38439,7 +38439,7 @@
         <v>46059</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38512,7 +38512,7 @@
         <v>46059</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38585,7 +38585,7 @@
         <v>46058</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>46059</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38731,7 +38731,7 @@
         <v>45418</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38804,7 +38804,7 @@
         <v>46063</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>45012</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38950,7 +38950,7 @@
         <v>46064</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39023,7 +39023,7 @@
         <v>46065</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>46181</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39169,7 +39169,7 @@
         <v>46181</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39242,7 +39242,7 @@
         <v>46181</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>46065</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>44973</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39461,7 +39461,7 @@
         <v>45450</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>46182</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>46181</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39690,7 +39690,7 @@
         <v>44691</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>46181</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>46072</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>46078</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39987,7 +39987,7 @@
         <v>46183</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40060,7 +40060,7 @@
         <v>46077</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>46078</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40206,7 +40206,7 @@
         <v>46185</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45952</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40357,7 +40357,7 @@
         <v>45989</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>46080</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>46080</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40576,7 +40576,7 @@
         <v>46080</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40649,7 +40649,7 @@
         <v>46083</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>46083</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40805,7 +40805,7 @@
         <v>46083</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40883,7 +40883,7 @@
         <v>44471</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>46185</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41034,7 +41034,7 @@
         <v>46185</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>45360</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>46185</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>45665</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>46090</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41414,7 +41414,7 @@
         <v>45307</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>46185</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>46185</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>46185</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>45247</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>46185</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41872,7 +41872,7 @@
         <v>44854</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41950,7 +41950,7 @@
         <v>46190</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>45613</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42096,7 +42096,7 @@
         <v>44944</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>46190</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42242,7 +42242,7 @@
         <v>45114</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42315,7 +42315,7 @@
         <v>46190</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>45586</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>45212</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>46195</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42612,7 +42612,7 @@
         <v>46195</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>45204</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>46195</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42841,7 +42841,7 @@
         <v>45385</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42914,7 +42914,7 @@
         <v>46106</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42987,7 +42987,7 @@
         <v>46108</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43060,7 +43060,7 @@
         <v>44641</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>45407</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43206,7 +43206,7 @@
         <v>45407</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>46108</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43352,7 +43352,7 @@
         <v>44615</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>46198</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43503,7 +43503,7 @@
         <v>46108</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43576,7 +43576,7 @@
         <v>46199</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43649,7 +43649,7 @@
         <v>44568</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43722,7 +43722,7 @@
         <v>45196</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>46244</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45356</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>46199</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44019,7 +44019,7 @@
         <v>46113</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44092,7 +44092,7 @@
         <v>45488</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>46245</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44248,7 +44248,7 @@
         <v>45523</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44321,7 +44321,7 @@
         <v>45523</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>46245</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44472,7 +44472,7 @@
         <v>46125</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44545,7 +44545,7 @@
         <v>46244</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44618,7 +44618,7 @@
         <v>45372</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>46127</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>46128</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>46199</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>46132</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>46133</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>46133</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>46204</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45217,7 +45217,7 @@
         <v>45210</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45290,7 +45290,7 @@
         <v>46132</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>46131</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         <v>46133</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45509,7 +45509,7 @@
         <v>46246</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45582,7 +45582,7 @@
         <v>46133</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>46203</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45733,7 +45733,7 @@
         <v>46135</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45607</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>46135</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>46135</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>46135</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46098,7 +46098,7 @@
         <v>46135</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>46135</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>46135</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>45278</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46390,7 +46390,7 @@
         <v>45602</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45265</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>45216</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>46139</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>45258</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>45407</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46828,7 +46828,7 @@
         <v>44574</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46901,7 +46901,7 @@
         <v>46246</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46974,7 +46974,7 @@
         <v>46204</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47052,7 +47052,7 @@
         <v>45603</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47130,7 +47130,7 @@
         <v>46246</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47203,7 +47203,7 @@
         <v>44923</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>45586</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>46247</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>46246</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>46246</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>45210</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47646,7 +47646,7 @@
         <v>45709</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>46248</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47797,7 +47797,7 @@
         <v>46146</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>45770</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>46251</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>46245</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>46246</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48172,7 +48172,7 @@
         <v>46206</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>46206</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48328,7 +48328,7 @@
         <v>44988</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>46206</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45163</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48557,7 +48557,7 @@
         <v>45371</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48635,7 +48635,7 @@
         <v>46167</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48713,7 +48713,7 @@
         <v>46251</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>45427</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>46251</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48937,7 +48937,7 @@
         <v>46251</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49015,7 +49015,7 @@
         <v>46252</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49088,7 +49088,7 @@
         <v>46210</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49166,7 +49166,7 @@
         <v>45671</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>45631</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         <v>45136</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>45475</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49458,7 +49458,7 @@
         <v>46253</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49536,7 +49536,7 @@
         <v>46210</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49614,7 +49614,7 @@
         <v>46252</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49687,7 +49687,7 @@
         <v>46252</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>46209</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49843,7 +49843,7 @@
         <v>46178</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>46209</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49999,7 +49999,7 @@
         <v>44988</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50072,7 +50072,7 @@
         <v>46212</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50150,7 +50150,7 @@
         <v>46212</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50228,7 +50228,7 @@
         <v>46254</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>46254</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50384,7 +50384,7 @@
         <v>46212</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50462,7 +50462,7 @@
         <v>46212</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50540,7 +50540,7 @@
         <v>46212</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50618,7 +50618,7 @@
         <v>45309</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45309</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50774,7 +50774,7 @@
         <v>45541</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50852,7 +50852,7 @@
         <v>45630</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50925,7 +50925,7 @@
         <v>44832</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50998,7 +50998,7 @@
         <v>46214</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51071,7 +51071,7 @@
         <v>45583</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51149,7 +51149,7 @@
         <v>46157</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51227,7 +51227,7 @@
         <v>44959</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51300,7 +51300,7 @@
         <v>44743</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51373,7 +51373,7 @@
         <v>45884</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51451,7 +51451,7 @@
         <v>46258</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51529,7 +51529,7 @@
         <v>46204</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>46157</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>46258</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51763,7 +51763,7 @@
         <v>46248</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51841,7 +51841,7 @@
         <v>45831</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51919,7 +51919,7 @@
         <v>46258</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51997,7 +51997,7 @@
         <v>46258</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52075,7 +52075,7 @@
         <v>46258</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52153,7 +52153,7 @@
         <v>44892</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>46148</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45957</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>44959</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52460,7 +52460,7 @@
         <v>46258</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>46258</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52616,7 +52616,7 @@
         <v>46261</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52694,7 +52694,7 @@
         <v>45463</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52772,7 +52772,7 @@
         <v>45491</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52845,7 +52845,7 @@
         <v>45621</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52918,7 +52918,7 @@
         <v>45418</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52991,7 +52991,7 @@
         <v>45585</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53064,7 +53064,7 @@
         <v>45548</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>44968</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53210,7 +53210,7 @@
         <v>45251</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53283,7 +53283,7 @@
         <v>46265</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53356,7 +53356,7 @@
         <v>45583</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53434,7 +53434,7 @@
         <v>45566</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53507,7 +53507,7 @@
         <v>44824</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53580,7 +53580,7 @@
         <v>46265</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>46265</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53726,7 +53726,7 @@
         <v>46265</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53799,7 +53799,7 @@
         <v>46266</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53872,7 +53872,7 @@
         <v>45736</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53945,7 +53945,7 @@
         <v>46223</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54018,7 +54018,7 @@
         <v>46223</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54091,7 +54091,7 @@
         <v>45630</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54164,7 +54164,7 @@
         <v>46223</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54237,7 +54237,7 @@
         <v>46223</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54310,7 +54310,7 @@
         <v>46223</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54383,7 +54383,7 @@
         <v>46267</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54461,7 +54461,7 @@
         <v>45162</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54534,7 +54534,7 @@
         <v>46266</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54607,7 +54607,7 @@
         <v>45592</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54680,7 +54680,7 @@
         <v>46225</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54758,7 +54758,7 @@
         <v>45033</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54831,7 +54831,7 @@
         <v>46225</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54909,7 +54909,7 @@
         <v>46225</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54987,7 +54987,7 @@
         <v>46225</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55065,7 +55065,7 @@
         <v>46225</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55143,7 +55143,7 @@
         <v>46225</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55221,7 +55221,7 @@
         <v>46225</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55299,7 +55299,7 @@
         <v>46226</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55372,7 +55372,7 @@
         <v>45236</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55445,7 +55445,7 @@
         <v>45777</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55518,7 +55518,7 @@
         <v>45777</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>45558</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55664,7 +55664,7 @@
         <v>45782</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55737,7 +55737,7 @@
         <v>45780</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55810,7 +55810,7 @@
         <v>46273</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>46227</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55961,7 +55961,7 @@
         <v>46273</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56034,7 +56034,7 @@
         <v>46134</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56107,7 +56107,7 @@
         <v>46273</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56180,7 +56180,7 @@
         <v>46231</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56253,7 +56253,7 @@
         <v>46274</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56331,7 +56331,7 @@
         <v>46274</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56404,7 +56404,7 @@
         <v>46274</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56477,7 +56477,7 @@
         <v>46198</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56550,7 +56550,7 @@
         <v>46274</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56623,7 +56623,7 @@
         <v>46275</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56701,7 +56701,7 @@
         <v>46279</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56774,7 +56774,7 @@
         <v>46132</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56847,7 +56847,7 @@
         <v>46279</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         <v>46237</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56993,7 +56993,7 @@
         <v>46234</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57066,7 +57066,7 @@
         <v>46237</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57139,7 +57139,7 @@
         <v>46234</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57212,7 +57212,7 @@
         <v>46234</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57285,7 +57285,7 @@
         <v>45006</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57363,7 +57363,7 @@
         <v>46276</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57436,7 +57436,7 @@
         <v>45002</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>46274</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57587,7 +57587,7 @@
         <v>46281</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57665,7 +57665,7 @@
         <v>46265</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57738,7 +57738,7 @@
         <v>46274</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57811,7 +57811,7 @@
         <v>46280</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57884,7 +57884,7 @@
         <v>46243</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57957,7 +57957,7 @@
         <v>46274</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>46280</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58108,7 +58108,7 @@
         <v>46280</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58181,7 +58181,7 @@
         <v>46280</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58259,7 +58259,7 @@
         <v>46280</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58337,7 +58337,7 @@
         <v>46280</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>46240</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58488,7 +58488,7 @@
         <v>46241</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58561,7 +58561,7 @@
         <v>46240</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58634,7 +58634,7 @@
         <v>45794</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58707,7 +58707,7 @@
         <v>46239</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58785,7 +58785,7 @@
         <v>45796</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58863,7 +58863,7 @@
         <v>46241</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58941,7 +58941,7 @@
         <v>46206</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59014,7 +59014,7 @@
         <v>46243</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59087,7 +59087,7 @@
         <v>46282</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59165,7 +59165,7 @@
         <v>45801</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59238,7 +59238,7 @@
         <v>44860</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59311,7 +59311,7 @@
         <v>45807</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59389,7 +59389,7 @@
         <v>44791</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59462,7 +59462,7 @@
         <v>45712</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59535,7 +59535,7 @@
         <v>45002</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59613,7 +59613,7 @@
         <v>45399</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59686,7 +59686,7 @@
         <v>45736</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59759,7 +59759,7 @@
         <v>45821</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59837,7 +59837,7 @@
         <v>45820</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59910,7 +59910,7 @@
         <v>45820</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59983,7 +59983,7 @@
         <v>45820</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60061,7 +60061,7 @@
         <v>45472</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60134,7 +60134,7 @@
         <v>45820</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60207,7 +60207,7 @@
         <v>45472</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60280,7 +60280,7 @@
         <v>45827</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60358,7 +60358,7 @@
         <v>45832</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60436,7 +60436,7 @@
         <v>45838</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60514,7 +60514,7 @@
         <v>45838</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60592,7 +60592,7 @@
         <v>45840</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60670,7 +60670,7 @@
         <v>45841</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60743,7 +60743,7 @@
         <v>45840</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60821,7 +60821,7 @@
         <v>45849</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60899,7 +60899,7 @@
         <v>45849</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60977,7 +60977,7 @@
         <v>45855</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61055,7 +61055,7 @@
         <v>45856</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61128,7 +61128,7 @@
         <v>45863</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61201,7 +61201,7 @@
         <v>45868</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61279,7 +61279,7 @@
         <v>45873</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61352,7 +61352,7 @@
         <v>45873</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61425,7 +61425,7 @@
         <v>45877</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61498,7 +61498,7 @@
         <v>45877</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61571,7 +61571,7 @@
         <v>45880</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61644,7 +61644,7 @@
         <v>45475</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61717,7 +61717,7 @@
         <v>45880</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61790,7 +61790,7 @@
         <v>45880</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>45882</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61946,7 +61946,7 @@
         <v>45882</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62024,7 +62024,7 @@
         <v>45882</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62102,7 +62102,7 @@
         <v>45461</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62180,7 +62180,7 @@
         <v>45393</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62258,7 +62258,7 @@
         <v>44579</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62331,7 +62331,7 @@
         <v>44741</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62404,7 +62404,7 @@
         <v>44960</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62482,7 +62482,7 @@
         <v>44691</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62555,7 +62555,7 @@
         <v>44958</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62628,7 +62628,7 @@
         <v>44578</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62701,7 +62701,7 @@
         <v>44578</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62774,7 +62774,7 @@
         <v>44691</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62847,7 +62847,7 @@
         <v>45729</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62925,7 +62925,7 @@
         <v>45782</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63003,7 +63003,7 @@
         <v>45821</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63081,7 +63081,7 @@
         <v>45821</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63159,7 +63159,7 @@
         <v>45796</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63232,7 +63232,7 @@
         <v>45841</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63310,7 +63310,7 @@
         <v>46080</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63383,7 +63383,7 @@
         <v>46125</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63461,7 +63461,7 @@
         <v>46125</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63539,7 +63539,7 @@
         <v>46129</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63617,7 +63617,7 @@
         <v>46135</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63690,7 +63690,7 @@
         <v>46135</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63763,7 +63763,7 @@
         <v>46135</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63836,7 +63836,7 @@
         <v>46174</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63909,7 +63909,7 @@
         <v>46176</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63982,7 +63982,7 @@
         <v>46252</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>

--- a/Översikt PAJALA.xlsx
+++ b/Översikt PAJALA.xlsx
@@ -601,7 +601,7 @@
         <v>45880</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>44874</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>45749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45345</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>44503</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>46197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>45407</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45845</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44608</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>45306</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>46171</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>44588</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>45405</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>44608</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>45981</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>46258</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>46260</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>44487</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44874</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>44608</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>44608</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44893</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>45964</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>45841</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>44608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>46211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>45671</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>44943</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44503</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>46029</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>45902</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>46182</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>46182</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>46254</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>46212</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>45469</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>45499</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>46052</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>45959</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>45530</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>45957</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44760</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>44755</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>44513</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>44608</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>45196</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>44945</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>45973</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>45476</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>45769</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>45643</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>46253</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>45392</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>44895</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45530</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>46237</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>45215</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>46034</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>45897</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>46107</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>45902</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>45755</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45150</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>44930</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>46178</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>46182</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>46196</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>44771</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>45163</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>46204</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>46178</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>46216</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>46258</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>46274</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>46273</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>46275</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>46237</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>44964</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>44496</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>45254</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>44854</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>44854</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>46035</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>45894</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>45894</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>45356</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>45575</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>45938</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>46125</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>46128</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>45722</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>45820</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>45832</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>46153</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
         <v>45838</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>46188</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>45585</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>45585</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>46189</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>46189</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>45875</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>46204</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>46251</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44608</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>46196</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>46227</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>46276</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>45121</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>45216</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         <v>45497</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>45611</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>45791</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>44579</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>45394</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>44755</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>44691</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>44532</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>44476</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>44691</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>44755</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>44755</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>44755</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44602</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>44523</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>44691</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>44691</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>44691</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>44496</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>44700</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>44756</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>44622</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>44837</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>44879</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>44884</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>44627</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44642</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>44875</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>44691</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>44629</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>44592</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>44634</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         <v>44663</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>44869</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         <v>44627</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         <v>44873</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
         <v>44873</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44518</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>44834</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>44663</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44550</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>44552</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44796</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>44749</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>44663</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>44521</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16798,7 +16798,7 @@
         <v>44860</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         <v>44862</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>44627</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>44691</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>45334</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>45215</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>44743</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>45334</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>45434</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>45210</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>45270</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>45450</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>44477</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>45418</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>45360</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44960</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45454</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44574</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>45477</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>44517</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>45463</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>45796</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>45794</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>45884</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>46020</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>44854</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>45247</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>46020</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>44471</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18955,7 +18955,7 @@
         <v>46021</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>46021</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19101,7 +19101,7 @@
         <v>45271</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
         <v>44894</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>45154</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>46029</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>46029</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>46030</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>46029</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>46029</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44790</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>44970</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45455</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>45314</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>45491</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>45469</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>46029</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>46031</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         <v>46031</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>46034</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>44973</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>44884</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>45033</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45894</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>46038</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>45895</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>45898</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45897</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>44874</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>45621</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>45603</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>45898</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>45597</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21414,7 +21414,7 @@
         <v>45475</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>46048</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45902</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>45899</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>45902</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>45566</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>46049</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>46049</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>45906</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45560</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>46052</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45905</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22320,7 +22320,7 @@
         <v>45909</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22393,7 +22393,7 @@
         <v>45909</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>45557</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>46058</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45914</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>46059</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>46059</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>45447</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>46059</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>46059</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>45918</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>46063</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>45918</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>45418</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>45922</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>45919</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>45919</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>45919</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>46065</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>46064</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>46065</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>44959</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45923</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45801</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45217</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>45923</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>45926</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>45925</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>44860</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>46072</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>46077</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>46078</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45925</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45989</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>45952</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>46078</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>46083</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>46083</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>46083</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>45488</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>45586</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>46080</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>46080</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>46080</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>45807</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44791</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25733,7 +25733,7 @@
         <v>45936</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>45934</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         <v>45058</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>45936</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>45936</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>45936</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26171,7 +26171,7 @@
         <v>45936</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26249,7 +26249,7 @@
         <v>46090</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>45938</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>44578</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>45671</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>45870</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>44923</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45938</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>45939</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>45938</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>45938</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>45938</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>45943</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>45944</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>45943</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>45764</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>44755</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>45002</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45177</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>44973</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>44959</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>45558</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>45251</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>44988</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>46106</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>46108</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>44968</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>45399</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>46108</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>46108</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45712</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>45944</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>46113</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>45623</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>45964</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45964</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>46125</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>45965</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>44860</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>45968</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>45968</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>45968</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>45583</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29345,7 +29345,7 @@
         <v>45972</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>45972</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45972</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>45970</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29637,7 +29637,7 @@
         <v>45972</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29710,7 +29710,7 @@
         <v>45972</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>45972</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29856,7 +29856,7 @@
         <v>45972</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>45972</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>45972</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>45972</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>45971</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>45972</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>45972</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>45736</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>46127</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>45631</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>46128</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>46132</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30742,7 +30742,7 @@
         <v>46132</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>45975</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>45980</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>46131</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>44832</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>46133</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>46133</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>45981</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>46133</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>45981</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31477,7 +31477,7 @@
         <v>46133</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>45981</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31623,7 +31623,7 @@
         <v>45631</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>46134</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31769,7 +31769,7 @@
         <v>45210</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>45665</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>46135</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31988,7 +31988,7 @@
         <v>46135</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>46136</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>46135</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>45988</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>46135</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>46135</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>46135</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>46136</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>46135</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>45740</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>45862</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44778</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>45736</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>45196</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>45995</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>45592</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>44756</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33239,7 +33239,7 @@
         <v>46139</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>44504</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>45152</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>46002</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>46002</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>46002</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>46002</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>46002</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>46002</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33916,7 +33916,7 @@
         <v>46006</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>46006</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34062,7 +34062,7 @@
         <v>45443</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>46006</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34213,7 +34213,7 @@
         <v>45820</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>45820</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>45820</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34437,7 +34437,7 @@
         <v>45162</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34510,7 +34510,7 @@
         <v>45820</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34583,7 +34583,7 @@
         <v>45821</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34661,7 +34661,7 @@
         <v>45472</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34734,7 +34734,7 @@
         <v>45472</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>45212</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34880,7 +34880,7 @@
         <v>45698</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>45910</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>44916</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>45265</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>45827</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>45180</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>46146</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>45054</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35469,7 +35469,7 @@
         <v>45599</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35547,7 +35547,7 @@
         <v>45540</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>45832</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35698,7 +35698,7 @@
         <v>46147</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>44910</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>44892</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>44755</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>44467</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36073,7 +36073,7 @@
         <v>46155</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>45391</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>45838</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>45838</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36380,7 +36380,7 @@
         <v>45275</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>44968</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36526,7 +36526,7 @@
         <v>46162</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>44892</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>45840</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36750,7 +36750,7 @@
         <v>45841</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36823,7 +36823,7 @@
         <v>45307</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44968</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
         <v>46162</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37042,7 +37042,7 @@
         <v>46162</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>45443</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>46161</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37261,7 +37261,7 @@
         <v>45878</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
         <v>45960</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45970</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>45972</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>45849</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37631,7 +37631,7 @@
         <v>45849</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>45960</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37782,7 +37782,7 @@
         <v>44568</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>45736</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>45371</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>45856</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38079,7 +38079,7 @@
         <v>45770</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38152,7 +38152,7 @@
         <v>45855</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38230,7 +38230,7 @@
         <v>45265</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>46173</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>46173</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38449,7 +38449,7 @@
         <v>46171</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>46170</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38600,7 +38600,7 @@
         <v>44908</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>44944</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>45863</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38819,7 +38819,7 @@
         <v>45427</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>45868</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45505</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>46177</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45114</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>46181</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>46181</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>45523</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>46181</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>45970</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>45611</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>46182</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39710,7 +39710,7 @@
         <v>45454</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39783,7 +39783,7 @@
         <v>46181</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>46181</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>46181</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40002,7 +40002,7 @@
         <v>46181</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>46181</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40148,7 +40148,7 @@
         <v>44988</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>46183</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>46185</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>46185</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40450,7 +40450,7 @@
         <v>45873</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40523,7 +40523,7 @@
         <v>46185</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>45678</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>46185</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40752,7 +40752,7 @@
         <v>46185</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>46185</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40908,7 +40908,7 @@
         <v>46185</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40986,7 +40986,7 @@
         <v>46185</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>45873</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41137,7 +41137,7 @@
         <v>46190</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>45592</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>45592</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>46190</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         <v>46190</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>45486</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>45613</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>46195</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>45481</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>46195</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>46195</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41955,7 +41955,7 @@
         <v>45877</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42028,7 +42028,7 @@
         <v>45589</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42101,7 +42101,7 @@
         <v>45475</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42174,7 +42174,7 @@
         <v>45880</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>45630</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>44568</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>45877</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42471,7 +42471,7 @@
         <v>45880</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42544,7 +42544,7 @@
         <v>45631</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42617,7 +42617,7 @@
         <v>44641</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>45880</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>46199</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42836,7 +42836,7 @@
         <v>45585</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>46199</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
         <v>44552</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43060,7 +43060,7 @@
         <v>46199</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43138,7 +43138,7 @@
         <v>46198</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>45491</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>45882</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43367,7 +43367,7 @@
         <v>45579</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43440,7 +43440,7 @@
         <v>45579</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45882</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43591,7 +43591,7 @@
         <v>46203</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>45660</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45660</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>45407</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>45407</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>45882</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>46204</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>45064</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>46204</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>46167</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>45163</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44424,7 +44424,7 @@
         <v>45372</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>46209</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>46206</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44658,7 +44658,7 @@
         <v>46206</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>46252</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44809,7 +44809,7 @@
         <v>46252</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44882,7 +44882,7 @@
         <v>46252</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44960,7 +44960,7 @@
         <v>46209</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
         <v>46251</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45111,7 +45111,7 @@
         <v>46146</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>46206</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>46251</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>46251</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45418,7 +45418,7 @@
         <v>45667</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>46251</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45569,7 +45569,7 @@
         <v>45407</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45642,7 +45642,7 @@
         <v>46210</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45720,7 +45720,7 @@
         <v>46253</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>44691</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>46254</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45949,7 +45949,7 @@
         <v>46178</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>46210</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46105,7 +46105,7 @@
         <v>46254</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46183,7 +46183,7 @@
         <v>46212</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>46212</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>45131</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>46157</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>46204</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46568,7 +46568,7 @@
         <v>45541</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46646,7 +46646,7 @@
         <v>45957</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>44874</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>45831</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>46214</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>46212</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>45630</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>46212</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>46148</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47260,7 +47260,7 @@
         <v>45583</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>45177</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>46212</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>46157</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45884</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>45583</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>44615</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>46258</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47874,7 +47874,7 @@
         <v>46258</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47952,7 +47952,7 @@
         <v>46258</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48030,7 +48030,7 @@
         <v>45523</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>45709</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45387</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48254,7 +48254,7 @@
         <v>46258</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48332,7 +48332,7 @@
         <v>45136</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48405,7 +48405,7 @@
         <v>46258</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48483,7 +48483,7 @@
         <v>46258</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48561,7 +48561,7 @@
         <v>46258</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48639,7 +48639,7 @@
         <v>45187</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>45630</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48785,7 +48785,7 @@
         <v>45548</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>46261</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48936,7 +48936,7 @@
         <v>44841</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>46265</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49082,7 +49082,7 @@
         <v>46265</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>46266</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49228,7 +49228,7 @@
         <v>46223</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>46223</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49374,7 +49374,7 @@
         <v>46265</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>46266</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>46223</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49593,7 +49593,7 @@
         <v>46223</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49666,7 +49666,7 @@
         <v>46265</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49739,7 +49739,7 @@
         <v>46223</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>46225</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49890,7 +49890,7 @@
         <v>46225</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49968,7 +49968,7 @@
         <v>46225</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50046,7 +50046,7 @@
         <v>46225</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45316</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50197,7 +50197,7 @@
         <v>45309</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50275,7 +50275,7 @@
         <v>45227</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50348,7 +50348,7 @@
         <v>46267</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>46225</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50504,7 +50504,7 @@
         <v>46225</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>46225</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50660,7 +50660,7 @@
         <v>45440</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50733,7 +50733,7 @@
         <v>46227</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50806,7 +50806,7 @@
         <v>46134</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50879,7 +50879,7 @@
         <v>44861</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>46226</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51030,7 +51030,7 @@
         <v>45477</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51103,7 +51103,7 @@
         <v>45482</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51176,7 +51176,7 @@
         <v>46273</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51254,7 +51254,7 @@
         <v>45210</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51327,7 +51327,7 @@
         <v>46274</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45238</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51478,7 +51478,7 @@
         <v>45238</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51551,7 +51551,7 @@
         <v>46274</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51624,7 +51624,7 @@
         <v>46274</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51697,7 +51697,7 @@
         <v>46273</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51770,7 +51770,7 @@
         <v>44824</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51843,7 +51843,7 @@
         <v>46274</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51916,7 +51916,7 @@
         <v>46198</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51989,7 +51989,7 @@
         <v>46231</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52062,7 +52062,7 @@
         <v>46273</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52135,7 +52135,7 @@
         <v>44834</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>46276</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52281,7 +52281,7 @@
         <v>45258</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>46275</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52432,7 +52432,7 @@
         <v>45616</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52505,7 +52505,7 @@
         <v>45136</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>46280</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52656,7 +52656,7 @@
         <v>46279</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52729,7 +52729,7 @@
         <v>46234</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52802,7 +52802,7 @@
         <v>46280</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52875,7 +52875,7 @@
         <v>46280</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52953,7 +52953,7 @@
         <v>46237</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53026,7 +53026,7 @@
         <v>46280</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53104,7 +53104,7 @@
         <v>46280</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53182,7 +53182,7 @@
         <v>46280</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53255,7 +53255,7 @@
         <v>46237</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53328,7 +53328,7 @@
         <v>46234</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53401,7 +53401,7 @@
         <v>46279</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53474,7 +53474,7 @@
         <v>46234</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>45247</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53620,7 +53620,7 @@
         <v>46274</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>46240</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53766,7 +53766,7 @@
         <v>46282</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53844,7 +53844,7 @@
         <v>46239</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53922,7 +53922,7 @@
         <v>46265</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>46274</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54068,7 +54068,7 @@
         <v>46240</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54141,7 +54141,7 @@
         <v>45523</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54214,7 +54214,7 @@
         <v>45523</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54287,7 +54287,7 @@
         <v>46281</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54365,7 +54365,7 @@
         <v>46206</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54438,7 +54438,7 @@
         <v>46274</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>45406</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>46286</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54662,7 +54662,7 @@
         <v>46241</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54740,7 +54740,7 @@
         <v>46243</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54813,7 +54813,7 @@
         <v>46241</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54886,7 +54886,7 @@
         <v>45974</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54959,7 +54959,7 @@
         <v>44518</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55032,7 +55032,7 @@
         <v>45611</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55105,7 +55105,7 @@
         <v>44522</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55178,7 +55178,7 @@
         <v>45356</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55251,7 +55251,7 @@
         <v>45370</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55324,7 +55324,7 @@
         <v>45062</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>46244</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55470,7 +55470,7 @@
         <v>45925</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55543,7 +55543,7 @@
         <v>46245</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55621,7 +55621,7 @@
         <v>45566</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55694,7 +55694,7 @@
         <v>44804</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55767,7 +55767,7 @@
         <v>46288</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55845,7 +55845,7 @@
         <v>44988</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55918,7 +55918,7 @@
         <v>46246</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55991,7 +55991,7 @@
         <v>46132</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56064,7 +56064,7 @@
         <v>45930</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56137,7 +56137,7 @@
         <v>46245</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56215,7 +56215,7 @@
         <v>46284</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56288,7 +56288,7 @@
         <v>44960</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>44960</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56444,7 +56444,7 @@
         <v>45586</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56517,7 +56517,7 @@
         <v>45586</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56590,7 +56590,7 @@
         <v>46244</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56663,7 +56663,7 @@
         <v>46245</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56741,7 +56741,7 @@
         <v>45356</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56814,7 +56814,7 @@
         <v>46248</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56892,7 +56892,7 @@
         <v>46248</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56970,7 +56970,7 @@
         <v>46247</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57048,7 +57048,7 @@
         <v>45707</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57121,7 +57121,7 @@
         <v>46246</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57194,7 +57194,7 @@
         <v>46246</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57267,7 +57267,7 @@
         <v>46246</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57340,7 +57340,7 @@
         <v>45216</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57413,7 +57413,7 @@
         <v>44958</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57486,7 +57486,7 @@
         <v>46246</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57559,7 +57559,7 @@
         <v>46146</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57632,7 +57632,7 @@
         <v>46246</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57705,7 +57705,7 @@
         <v>46289</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57783,7 +57783,7 @@
         <v>45777</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57856,7 +57856,7 @@
         <v>44547</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57929,7 +57929,7 @@
         <v>45031</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58002,7 +58002,7 @@
         <v>45602</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>44608</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58153,7 +58153,7 @@
         <v>45475</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58226,7 +58226,7 @@
         <v>45575</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58299,7 +58299,7 @@
         <v>45012</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45607</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58445,7 +58445,7 @@
         <v>45467</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58518,7 +58518,7 @@
         <v>45630</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58591,7 +58591,7 @@
         <v>45613</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58664,7 +58664,7 @@
         <v>45012</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58737,7 +58737,7 @@
         <v>45309</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58815,7 +58815,7 @@
         <v>45592</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45611</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58961,7 +58961,7 @@
         <v>44968</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59034,7 +59034,7 @@
         <v>45218</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59107,7 +59107,7 @@
         <v>45204</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59180,7 +59180,7 @@
         <v>45201</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59253,7 +59253,7 @@
         <v>45118</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59326,7 +59326,7 @@
         <v>45611</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59399,7 +59399,7 @@
         <v>45169</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59477,7 +59477,7 @@
         <v>45278</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59550,7 +59550,7 @@
         <v>45474</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59623,7 +59623,7 @@
         <v>45463</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59701,7 +59701,7 @@
         <v>45671</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59774,7 +59774,7 @@
         <v>45573</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59847,7 +59847,7 @@
         <v>45580</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59920,7 +59920,7 @@
         <v>45297</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59993,7 +59993,7 @@
         <v>45682</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60066,7 +60066,7 @@
         <v>45477</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>45498</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60212,7 +60212,7 @@
         <v>44892</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60285,7 +60285,7 @@
         <v>44837</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60358,7 +60358,7 @@
         <v>44889</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60431,7 +60431,7 @@
         <v>45385</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60504,7 +60504,7 @@
         <v>45603</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60582,7 +60582,7 @@
         <v>45624</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60655,7 +60655,7 @@
         <v>45601</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60733,7 +60733,7 @@
         <v>45227</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60806,7 +60806,7 @@
         <v>45665</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60879,7 +60879,7 @@
         <v>45427</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60952,7 +60952,7 @@
         <v>45236</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45780</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61098,7 +61098,7 @@
         <v>45782</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61171,7 +61171,7 @@
         <v>45558</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61244,7 +61244,7 @@
         <v>45002</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61322,7 +61322,7 @@
         <v>45006</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61400,7 +61400,7 @@
         <v>44579</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61473,7 +61473,7 @@
         <v>44691</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61546,7 +61546,7 @@
         <v>44578</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61619,7 +61619,7 @@
         <v>44578</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>44691</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61765,7 +61765,7 @@
         <v>45461</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61843,7 +61843,7 @@
         <v>45393</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61921,7 +61921,7 @@
         <v>44741</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61994,7 +61994,7 @@
         <v>44960</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62072,7 +62072,7 @@
         <v>44958</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62145,7 +62145,7 @@
         <v>45729</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62223,7 +62223,7 @@
         <v>45782</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62301,7 +62301,7 @@
         <v>45821</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62379,7 +62379,7 @@
         <v>45821</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62457,7 +62457,7 @@
         <v>45796</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62530,7 +62530,7 @@
         <v>45841</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62608,7 +62608,7 @@
         <v>46080</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62681,7 +62681,7 @@
         <v>46125</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62759,7 +62759,7 @@
         <v>46125</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62837,7 +62837,7 @@
         <v>46129</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62915,7 +62915,7 @@
         <v>46135</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62988,7 +62988,7 @@
         <v>46135</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63061,7 +63061,7 @@
         <v>46135</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63134,7 +63134,7 @@
         <v>46174</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63207,7 +63207,7 @@
         <v>46176</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63280,7 +63280,7 @@
         <v>46252</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>

--- a/Översikt PAJALA.xlsx
+++ b/Översikt PAJALA.xlsx
@@ -601,7 +601,7 @@
         <v>45880</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>44874</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>45749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45345</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>44503</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>46197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>45407</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45845</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44608</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>45306</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>46171</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>44588</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>45405</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>44608</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>45981</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>46258</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>46260</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>44487</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44874</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>44608</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>44608</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44893</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>45964</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>45841</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>44608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>46211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>45671</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>44943</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44503</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>46029</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>45902</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>46182</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>46182</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>46254</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>46212</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>45469</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>45499</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>46052</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>45959</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>45530</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>45957</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44760</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>44755</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>44513</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>44608</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>45196</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>44945</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>45973</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>45476</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>45769</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>45643</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>46253</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>45392</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>44895</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45530</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>46237</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>45215</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>46034</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>45897</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>46107</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>45902</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>45755</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45150</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>44930</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>46178</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>46182</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>46196</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>44771</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>45163</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>46204</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>46178</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>46216</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>46258</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>46274</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>46273</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>46275</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>46237</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>44964</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>44496</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>45254</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>44854</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>44854</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>46035</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>45894</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>45894</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>45356</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>45575</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>45938</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>46125</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>46128</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>45722</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>45820</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>45832</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>46153</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
         <v>45838</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>46188</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>45585</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>45585</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>46189</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>46189</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>45875</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>46204</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>46251</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44608</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>46196</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>46227</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>46276</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>45121</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>45216</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         <v>45497</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>45611</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>45791</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>44579</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>45394</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>44755</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>44691</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>44532</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>44476</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>44691</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>44755</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>44755</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>44755</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44602</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>44523</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>44691</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>44691</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>44691</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>44496</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>44700</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>44756</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>44622</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>44837</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>44879</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>44884</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>44627</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44642</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>44875</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>44691</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>44629</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>44592</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>44634</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         <v>44663</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>44869</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         <v>44627</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         <v>44873</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
         <v>44873</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44518</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>44834</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>44663</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44550</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>44552</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44796</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>44749</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>44663</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>44521</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16798,7 +16798,7 @@
         <v>44860</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         <v>44862</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>44627</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>44691</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>45334</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>45215</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>44743</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>45334</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>45434</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>45210</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>45270</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>45450</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>44477</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>45418</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>45360</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44960</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45454</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44574</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>45477</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>44517</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>45463</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>45796</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>45794</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>45884</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>46020</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>44854</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>45247</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>46020</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>44471</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18955,7 +18955,7 @@
         <v>46021</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>46021</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19101,7 +19101,7 @@
         <v>45271</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
         <v>44894</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>45154</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>46029</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>46029</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>46030</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>46029</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>46029</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44790</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>44970</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45455</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>45314</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>45491</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>45469</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>46029</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>46031</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         <v>46031</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>46034</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>44973</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>44884</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>45033</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45894</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>46038</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>45895</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>45898</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45897</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>44874</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>45621</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>45603</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>45898</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>45597</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21414,7 +21414,7 @@
         <v>45475</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>46048</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45902</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>45899</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>45902</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>45566</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>46049</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>46049</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>45906</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45560</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>46052</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45905</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22320,7 +22320,7 @@
         <v>45909</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22393,7 +22393,7 @@
         <v>45909</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>45557</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>46058</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45914</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>46059</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>46059</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>45447</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>46059</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>46059</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>45918</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>46063</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>45918</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>45418</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>45922</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>45919</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>45919</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>45919</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>46065</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>46064</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>46065</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>44959</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45923</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45801</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45217</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>45923</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>45926</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>45925</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>44860</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>46072</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>46077</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>46078</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45925</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45989</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>45952</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>46078</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>46083</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>46083</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>46083</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>45488</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>45586</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>46080</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>46080</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>46080</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>45807</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44791</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25733,7 +25733,7 @@
         <v>45936</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>45934</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         <v>45058</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>45936</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>45936</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>45936</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26171,7 +26171,7 @@
         <v>45936</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26249,7 +26249,7 @@
         <v>46090</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>45938</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>44578</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>45671</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>45870</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>44923</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45938</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>45939</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>45938</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>45938</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>45938</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>45943</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>45944</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>45943</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>45764</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>44755</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>45002</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45177</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>44973</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>44959</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>45558</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>45251</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>44988</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>46106</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>46108</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>44968</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>45399</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>46108</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>46108</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45712</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>45944</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>46113</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>45623</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>45964</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45964</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>46125</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>45965</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>44860</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>45968</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>45968</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>45968</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>45583</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29345,7 +29345,7 @@
         <v>45972</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>45972</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45972</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>45970</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29637,7 +29637,7 @@
         <v>45972</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29710,7 +29710,7 @@
         <v>45972</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>45972</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29856,7 +29856,7 @@
         <v>45972</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>45972</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>45972</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>45972</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>45971</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>45972</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>45972</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>45736</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>46127</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>45631</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>46128</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>46132</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30742,7 +30742,7 @@
         <v>46132</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>45975</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>45980</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>46131</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>44832</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>46133</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>46133</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>45981</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>46133</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>45981</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31477,7 +31477,7 @@
         <v>46133</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>45981</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31623,7 +31623,7 @@
         <v>45631</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>46134</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31769,7 +31769,7 @@
         <v>45210</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>45665</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>46135</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31988,7 +31988,7 @@
         <v>46135</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>46136</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>46135</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>45988</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>46135</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>46135</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>46135</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>46136</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>46135</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>45740</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>45862</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44778</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>45736</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>45196</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>45995</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>45592</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>44756</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33239,7 +33239,7 @@
         <v>46139</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>44504</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>45152</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>46002</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>46002</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>46002</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>46002</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>46002</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>46002</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33916,7 +33916,7 @@
         <v>46006</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>46006</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34062,7 +34062,7 @@
         <v>45443</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>46006</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34213,7 +34213,7 @@
         <v>45820</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>45820</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>45820</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34437,7 +34437,7 @@
         <v>45162</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34510,7 +34510,7 @@
         <v>45820</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34583,7 +34583,7 @@
         <v>45821</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34661,7 +34661,7 @@
         <v>45472</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34734,7 +34734,7 @@
         <v>45472</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>45212</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34880,7 +34880,7 @@
         <v>45698</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>45910</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>44916</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>45265</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>45827</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>45180</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>46146</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>45054</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35469,7 +35469,7 @@
         <v>45599</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35547,7 +35547,7 @@
         <v>45540</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>45832</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35698,7 +35698,7 @@
         <v>46147</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>44910</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>44892</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>44755</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>44467</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36073,7 +36073,7 @@
         <v>46155</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>45391</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>45838</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>45838</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36380,7 +36380,7 @@
         <v>45275</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>44968</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36526,7 +36526,7 @@
         <v>46162</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>44892</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>45840</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36750,7 +36750,7 @@
         <v>45841</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36823,7 +36823,7 @@
         <v>45307</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44968</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
         <v>46162</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37042,7 +37042,7 @@
         <v>46162</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>45443</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>46161</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37261,7 +37261,7 @@
         <v>45878</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
         <v>45960</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45970</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>45972</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>45849</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37631,7 +37631,7 @@
         <v>45849</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>45960</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37782,7 +37782,7 @@
         <v>44568</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37855,7 +37855,7 @@
         <v>45736</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>45371</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>45856</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38079,7 +38079,7 @@
         <v>45770</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38152,7 +38152,7 @@
         <v>45855</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38230,7 +38230,7 @@
         <v>45265</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>46173</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>46173</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38449,7 +38449,7 @@
         <v>46171</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>46170</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38600,7 +38600,7 @@
         <v>44908</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>44944</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>45863</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38819,7 +38819,7 @@
         <v>45427</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>45868</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45505</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>46177</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45114</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>46181</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>46181</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>45523</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>46181</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>45970</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>45611</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>46182</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39710,7 +39710,7 @@
         <v>45454</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39783,7 +39783,7 @@
         <v>46181</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>46181</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>46181</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40002,7 +40002,7 @@
         <v>46181</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>46181</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40148,7 +40148,7 @@
         <v>44988</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>46183</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>46185</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>46185</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40450,7 +40450,7 @@
         <v>45873</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40523,7 +40523,7 @@
         <v>46185</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>45678</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>46185</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40752,7 +40752,7 @@
         <v>46185</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>46185</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40908,7 +40908,7 @@
         <v>46185</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40986,7 +40986,7 @@
         <v>46185</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>45873</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41137,7 +41137,7 @@
         <v>46190</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>45592</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>45592</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>46190</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         <v>46190</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>45486</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>45613</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>46195</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>45481</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>46195</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>46195</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41955,7 +41955,7 @@
         <v>45877</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42028,7 +42028,7 @@
         <v>45589</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42101,7 +42101,7 @@
         <v>45475</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42174,7 +42174,7 @@
         <v>45880</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>45630</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>44568</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>45877</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42471,7 +42471,7 @@
         <v>45880</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42544,7 +42544,7 @@
         <v>45631</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42617,7 +42617,7 @@
         <v>44641</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>45880</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>46199</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42836,7 +42836,7 @@
         <v>45585</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>46199</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
         <v>44552</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43060,7 +43060,7 @@
         <v>46199</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43138,7 +43138,7 @@
         <v>46198</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>45491</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>45882</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43367,7 +43367,7 @@
         <v>45579</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43440,7 +43440,7 @@
         <v>45579</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45882</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43591,7 +43591,7 @@
         <v>46203</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>45660</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45660</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>45407</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>45407</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>45882</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>46204</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>45064</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>46204</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>46167</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>45163</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44424,7 +44424,7 @@
         <v>45372</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>46209</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>46206</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44658,7 +44658,7 @@
         <v>46206</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>46252</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44809,7 +44809,7 @@
         <v>46252</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44882,7 +44882,7 @@
         <v>46252</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44960,7 +44960,7 @@
         <v>46209</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
         <v>46251</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45111,7 +45111,7 @@
         <v>46146</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>46206</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>46251</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>46251</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45418,7 +45418,7 @@
         <v>45667</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>46251</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45569,7 +45569,7 @@
         <v>45407</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45642,7 +45642,7 @@
         <v>46210</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45720,7 +45720,7 @@
         <v>46253</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>44691</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>46254</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45949,7 +45949,7 @@
         <v>46178</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>46210</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46105,7 +46105,7 @@
         <v>46254</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46183,7 +46183,7 @@
         <v>46212</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>46212</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>45131</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>46157</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>46204</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46568,7 +46568,7 @@
         <v>45541</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46646,7 +46646,7 @@
         <v>45957</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>44874</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>45831</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>46214</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>46212</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>45630</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>46212</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>46148</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47260,7 +47260,7 @@
         <v>45583</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>45177</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>46212</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>46157</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45884</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>45583</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>44615</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>46258</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47874,7 +47874,7 @@
         <v>46258</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47952,7 +47952,7 @@
         <v>46258</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48030,7 +48030,7 @@
         <v>45523</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>45709</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45387</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48254,7 +48254,7 @@
         <v>46258</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48332,7 +48332,7 @@
         <v>45136</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48405,7 +48405,7 @@
         <v>46258</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48483,7 +48483,7 @@
         <v>46258</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48561,7 +48561,7 @@
         <v>46258</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48639,7 +48639,7 @@
         <v>45187</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>45630</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48785,7 +48785,7 @@
         <v>45548</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>46261</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48936,7 +48936,7 @@
         <v>44841</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>46265</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49082,7 +49082,7 @@
         <v>46265</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>46266</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49228,7 +49228,7 @@
         <v>46223</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>46223</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49374,7 +49374,7 @@
         <v>46265</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>46266</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>46223</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49593,7 +49593,7 @@
         <v>46223</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49666,7 +49666,7 @@
         <v>46265</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49739,7 +49739,7 @@
         <v>46223</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>46225</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49890,7 +49890,7 @@
         <v>46225</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49968,7 +49968,7 @@
         <v>46225</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50046,7 +50046,7 @@
         <v>46225</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45316</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50197,7 +50197,7 @@
         <v>45309</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50275,7 +50275,7 @@
         <v>45227</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50348,7 +50348,7 @@
         <v>46267</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>46225</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50504,7 +50504,7 @@
         <v>46225</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>46225</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50660,7 +50660,7 @@
         <v>45440</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50733,7 +50733,7 @@
         <v>46227</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50806,7 +50806,7 @@
         <v>46134</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50879,7 +50879,7 @@
         <v>44861</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>46226</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51030,7 +51030,7 @@
         <v>45477</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51103,7 +51103,7 @@
         <v>45482</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51176,7 +51176,7 @@
         <v>46273</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51254,7 +51254,7 @@
         <v>45210</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51327,7 +51327,7 @@
         <v>46274</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45238</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51478,7 +51478,7 @@
         <v>45238</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51551,7 +51551,7 @@
         <v>46274</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51624,7 +51624,7 @@
         <v>46274</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51697,7 +51697,7 @@
         <v>46273</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51770,7 +51770,7 @@
         <v>44824</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51843,7 +51843,7 @@
         <v>46274</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51916,7 +51916,7 @@
         <v>46198</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51989,7 +51989,7 @@
         <v>46231</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52062,7 +52062,7 @@
         <v>46273</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52135,7 +52135,7 @@
         <v>44834</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>46276</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52281,7 +52281,7 @@
         <v>45258</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>46275</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52432,7 +52432,7 @@
         <v>45616</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52505,7 +52505,7 @@
         <v>45136</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>46280</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52656,7 +52656,7 @@
         <v>46279</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52729,7 +52729,7 @@
         <v>46234</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52802,7 +52802,7 @@
         <v>46280</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52875,7 +52875,7 @@
         <v>46280</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52953,7 +52953,7 @@
         <v>46237</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53026,7 +53026,7 @@
         <v>46280</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53104,7 +53104,7 @@
         <v>46280</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53182,7 +53182,7 @@
         <v>46280</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53255,7 +53255,7 @@
         <v>46237</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53328,7 +53328,7 @@
         <v>46234</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53401,7 +53401,7 @@
         <v>46279</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53474,7 +53474,7 @@
         <v>46234</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>45247</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53620,7 +53620,7 @@
         <v>46274</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>46240</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53766,7 +53766,7 @@
         <v>46282</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53844,7 +53844,7 @@
         <v>46239</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53922,7 +53922,7 @@
         <v>46265</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>46274</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54068,7 +54068,7 @@
         <v>46240</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54141,7 +54141,7 @@
         <v>45523</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54214,7 +54214,7 @@
         <v>45523</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54287,7 +54287,7 @@
         <v>46281</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54365,7 +54365,7 @@
         <v>46206</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54438,7 +54438,7 @@
         <v>46274</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>45406</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>46286</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54662,7 +54662,7 @@
         <v>46241</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54740,7 +54740,7 @@
         <v>46243</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54813,7 +54813,7 @@
         <v>46241</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54886,7 +54886,7 @@
         <v>45974</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54959,7 +54959,7 @@
         <v>44518</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55032,7 +55032,7 @@
         <v>45611</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55105,7 +55105,7 @@
         <v>44522</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55178,7 +55178,7 @@
         <v>45356</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55251,7 +55251,7 @@
         <v>45370</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55324,7 +55324,7 @@
         <v>45062</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>46244</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55470,7 +55470,7 @@
         <v>45925</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55543,7 +55543,7 @@
         <v>46245</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55621,7 +55621,7 @@
         <v>45566</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55694,7 +55694,7 @@
         <v>44804</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55767,7 +55767,7 @@
         <v>46288</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55845,7 +55845,7 @@
         <v>44988</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55918,7 +55918,7 @@
         <v>46246</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55991,7 +55991,7 @@
         <v>46132</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56064,7 +56064,7 @@
         <v>45930</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56137,7 +56137,7 @@
         <v>46245</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56215,7 +56215,7 @@
         <v>46284</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56288,7 +56288,7 @@
         <v>44960</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>44960</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56444,7 +56444,7 @@
         <v>45586</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56517,7 +56517,7 @@
         <v>45586</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56590,7 +56590,7 @@
         <v>46244</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56663,7 +56663,7 @@
         <v>46245</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56741,7 +56741,7 @@
         <v>45356</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56814,7 +56814,7 @@
         <v>46248</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56892,7 +56892,7 @@
         <v>46248</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56970,7 +56970,7 @@
         <v>46247</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57048,7 +57048,7 @@
         <v>45707</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57121,7 +57121,7 @@
         <v>46246</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57194,7 +57194,7 @@
         <v>46246</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57267,7 +57267,7 @@
         <v>46246</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57340,7 +57340,7 @@
         <v>45216</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57413,7 +57413,7 @@
         <v>44958</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57486,7 +57486,7 @@
         <v>46246</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57559,7 +57559,7 @@
         <v>46146</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57632,7 +57632,7 @@
         <v>46246</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57705,7 +57705,7 @@
         <v>46289</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57783,7 +57783,7 @@
         <v>45777</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57856,7 +57856,7 @@
         <v>44547</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57929,7 +57929,7 @@
         <v>45031</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58002,7 +58002,7 @@
         <v>45602</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>44608</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58153,7 +58153,7 @@
         <v>45475</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58226,7 +58226,7 @@
         <v>45575</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58299,7 +58299,7 @@
         <v>45012</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45607</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58445,7 +58445,7 @@
         <v>45467</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58518,7 +58518,7 @@
         <v>45630</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58591,7 +58591,7 @@
         <v>45613</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58664,7 +58664,7 @@
         <v>45012</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58737,7 +58737,7 @@
         <v>45309</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58815,7 +58815,7 @@
         <v>45592</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45611</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58961,7 +58961,7 @@
         <v>44968</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59034,7 +59034,7 @@
         <v>45218</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59107,7 +59107,7 @@
         <v>45204</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59180,7 +59180,7 @@
         <v>45201</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59253,7 +59253,7 @@
         <v>45118</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59326,7 +59326,7 @@
         <v>45611</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59399,7 +59399,7 @@
         <v>45169</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59477,7 +59477,7 @@
         <v>45278</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59550,7 +59550,7 @@
         <v>45474</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59623,7 +59623,7 @@
         <v>45463</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59701,7 +59701,7 @@
         <v>45671</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59774,7 +59774,7 @@
         <v>45573</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59847,7 +59847,7 @@
         <v>45580</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59920,7 +59920,7 @@
         <v>45297</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59993,7 +59993,7 @@
         <v>45682</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60066,7 +60066,7 @@
         <v>45477</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>45498</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60212,7 +60212,7 @@
         <v>44892</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60285,7 +60285,7 @@
         <v>44837</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60358,7 +60358,7 @@
         <v>44889</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60431,7 +60431,7 @@
         <v>45385</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60504,7 +60504,7 @@
         <v>45603</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60582,7 +60582,7 @@
         <v>45624</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60655,7 +60655,7 @@
         <v>45601</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60733,7 +60733,7 @@
         <v>45227</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60806,7 +60806,7 @@
         <v>45665</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60879,7 +60879,7 @@
         <v>45427</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60952,7 +60952,7 @@
         <v>45236</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45780</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61098,7 +61098,7 @@
         <v>45782</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61171,7 +61171,7 @@
         <v>45558</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61244,7 +61244,7 @@
         <v>45002</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61322,7 +61322,7 @@
         <v>45006</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61400,7 +61400,7 @@
         <v>44579</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61473,7 +61473,7 @@
         <v>44691</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61546,7 +61546,7 @@
         <v>44578</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61619,7 +61619,7 @@
         <v>44578</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>44691</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61765,7 +61765,7 @@
         <v>45461</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61843,7 +61843,7 @@
         <v>45393</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61921,7 +61921,7 @@
         <v>44741</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61994,7 +61994,7 @@
         <v>44960</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62072,7 +62072,7 @@
         <v>44958</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62145,7 +62145,7 @@
         <v>45729</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62223,7 +62223,7 @@
         <v>45782</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62301,7 +62301,7 @@
         <v>45821</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62379,7 +62379,7 @@
         <v>45821</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62457,7 +62457,7 @@
         <v>45796</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62530,7 +62530,7 @@
         <v>45841</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62608,7 +62608,7 @@
         <v>46080</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62681,7 +62681,7 @@
         <v>46125</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62759,7 +62759,7 @@
         <v>46125</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62837,7 +62837,7 @@
         <v>46129</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62915,7 +62915,7 @@
         <v>46135</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62988,7 +62988,7 @@
         <v>46135</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63061,7 +63061,7 @@
         <v>46135</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63134,7 +63134,7 @@
         <v>46174</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63207,7 +63207,7 @@
         <v>46176</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63280,7 +63280,7 @@
         <v>46252</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>

--- a/Översikt PAJALA.xlsx
+++ b/Översikt PAJALA.xlsx
@@ -601,7 +601,7 @@
         <v>45880</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>44874</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>45749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45345</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>44503</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>46197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45407</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>45845</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>44608</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>45306</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>46171</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>44588</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>45405</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>45981</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>44608</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>46258</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>46260</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>44487</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>44608</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44874</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>44608</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>44893</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>45964</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>45841</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>46211</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>44608</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>46291</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>45671</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44943</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44503</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>46029</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>45902</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>46182</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>46182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>46212</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>46254</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>45469</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>45499</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>46052</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>45959</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>45957</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45530</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44760</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>44755</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44513</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>45392</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45643</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>44608</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>45973</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>44945</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>45476</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>46237</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>44895</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>45530</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45196</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>45769</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>44771</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45897</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>46034</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>45150</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>45902</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>46107</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>44930</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>46178</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>45163</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>46182</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>45755</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>46196</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>46204</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>46178</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>46258</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>46216</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>45215</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>44964</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>46225</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>46273</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>46274</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>46275</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>46237</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>44496</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>44608</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>45356</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>45791</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>45894</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>45894</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>46035</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>45938</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>45575</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>45585</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>45820</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>45722</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>46125</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>46128</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>45832</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>45838</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>45254</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>45611</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>45497</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>46153</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>45875</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>46188</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>46189</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>46189</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>45585</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>46204</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>46196</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>46227</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>46276</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>44854</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>44854</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>45121</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>46251</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>45216</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>44579</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>45394</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>46080</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>44755</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>44532</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>44691</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>44476</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
         <v>44691</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>44755</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>44755</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>44755</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>44602</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>44523</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>44691</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>44691</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>44691</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>44496</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44700</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>44756</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>44622</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15241,7 +15241,7 @@
         <v>44837</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>44884</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>44879</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>44627</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>44642</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>44875</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>44691</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>44629</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>44634</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15908,7 +15908,7 @@
         <v>44592</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>44663</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>44869</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>44627</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16200,7 +16200,7 @@
         <v>44873</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>44873</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>44518</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>44834</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>44663</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>44550</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>44552</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>44796</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>44749</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>44663</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>44521</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>44860</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>44862</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>44627</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>44691</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>45575</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>45467</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>45613</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>45275</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45698</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>45611</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>44804</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>44874</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>45454</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17972,7 +17972,7 @@
         <v>44504</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45238</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>45238</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         <v>45523</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>45006</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>44608</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>45611</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45002</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>46002</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>45884</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>46002</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>46002</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>45217</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>46002</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>46002</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>46002</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>46006</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>46006</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>46006</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>44960</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>44960</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>45054</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>44522</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>45477</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>46020</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>46021</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>46021</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>46020</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>45540</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20144,7 +20144,7 @@
         <v>45895</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>45665</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>45894</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>46029</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>46029</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>46029</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>46029</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>46029</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>45897</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20826,7 +20826,7 @@
         <v>45573</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>46031</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>46031</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>46030</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>45899</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>45898</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>45475</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>45898</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         <v>44756</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>46034</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>45902</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         <v>44874</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45902</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>45566</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>44892</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21946,7 +21946,7 @@
         <v>44517</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22019,7 +22019,7 @@
         <v>45905</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>46038</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>45906</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>45909</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>45909</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45794</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45796</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>45914</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>45169</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>44910</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22769,7 +22769,7 @@
         <v>46049</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>46048</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>45486</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>46049</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45201</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>45187</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>45918</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>45801</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>45919</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23441,7 +23441,7 @@
         <v>45919</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>45918</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>44860</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>45601</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45923</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>45592</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45807</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>45923</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45922</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45919</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>46052</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>45925</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>45925</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>45926</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>46059</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>46059</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45455</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>46059</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>46058</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>46059</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>46063</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>45678</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>45667</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>45469</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>46064</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>46065</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>46065</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>45936</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>45934</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45936</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>45936</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45936</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>45936</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>45938</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45938</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>45938</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>45671</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>45938</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26260,7 +26260,7 @@
         <v>45938</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>45227</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44477</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>45870</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>46072</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45939</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>45943</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45943</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45334</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>45944</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>46078</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>46077</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>45180</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44791</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>46078</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45952</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>45989</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>46080</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
         <v>45712</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27657,7 +27657,7 @@
         <v>46080</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>46080</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27803,7 +27803,7 @@
         <v>45477</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>46083</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>46083</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>45002</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         <v>46083</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>45505</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>45944</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>45399</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>46090</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>45965</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>45964</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28631,7 +28631,7 @@
         <v>45964</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>45154</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>45736</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>45334</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>45970</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>45583</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>45968</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>45971</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>45968</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>45972</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>45972</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>45227</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>44884</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>45972</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>45972</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>45972</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29809,7 +29809,7 @@
         <v>45972</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>45972</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>45972</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>45972</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>45972</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>45972</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30247,7 +30247,7 @@
         <v>45972</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30320,7 +30320,7 @@
         <v>45482</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>45975</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30466,7 +30466,7 @@
         <v>45447</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>46106</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30612,7 +30612,7 @@
         <v>46108</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30685,7 +30685,7 @@
         <v>45981</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>45981</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>45981</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>45631</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>45980</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>46108</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>46108</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>45387</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>45821</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>45820</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>45820</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>44894</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>45820</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>44916</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>45472</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>45820</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>45472</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>45764</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>44960</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>46113</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44547</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>45660</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45660</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>45988</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>45481</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>44568</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>45215</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>45557</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45827</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45740</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45995</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32983,7 +32983,7 @@
         <v>46125</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>46127</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45579</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>45579</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>46128</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33353,7 +33353,7 @@
         <v>45177</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>46132</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>46133</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>44973</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>46133</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33718,7 +33718,7 @@
         <v>46132</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
         <v>46131</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33864,7 +33864,7 @@
         <v>46133</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45474</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>45477</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>46133</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34156,7 +34156,7 @@
         <v>46135</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34229,7 +34229,7 @@
         <v>45832</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>46135</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>46135</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
         <v>46135</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34526,7 +34526,7 @@
         <v>46135</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34599,7 +34599,7 @@
         <v>46135</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34672,7 +34672,7 @@
         <v>45491</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         <v>46135</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34818,7 +34818,7 @@
         <v>45316</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>45454</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>45434</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>45838</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>45599</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>45603</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35271,7 +35271,7 @@
         <v>46139</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35344,7 +35344,7 @@
         <v>45838</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35422,7 +35422,7 @@
         <v>45840</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35500,7 +35500,7 @@
         <v>45841</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35573,7 +35573,7 @@
         <v>45849</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>45297</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35724,7 +35724,7 @@
         <v>45849</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>46136</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44968</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35948,7 +35948,7 @@
         <v>45855</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>44518</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36099,7 +36099,7 @@
         <v>44578</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36172,7 +36172,7 @@
         <v>45498</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36245,7 +36245,7 @@
         <v>45406</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36318,7 +36318,7 @@
         <v>45012</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>46134</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>44892</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>46136</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>45856</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>44861</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>45624</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>45177</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36907,7 +36907,7 @@
         <v>45623</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36980,7 +36980,7 @@
         <v>45910</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37053,7 +37053,7 @@
         <v>45863</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37126,7 +37126,7 @@
         <v>45616</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37199,7 +37199,7 @@
         <v>45118</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>45586</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37345,7 +37345,7 @@
         <v>45586</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>45580</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>45058</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>45152</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>45560</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45868</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37788,7 +37788,7 @@
         <v>44790</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>45862</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>45427</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>45630</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45218</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>46147</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38236,7 +38236,7 @@
         <v>46146</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45873</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38382,7 +38382,7 @@
         <v>45136</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>44988</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45592</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45592</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38674,7 +38674,7 @@
         <v>45682</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38747,7 +38747,7 @@
         <v>45265</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>45247</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>44755</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38966,7 +38966,7 @@
         <v>46155</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>44778</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>44755</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39190,7 +39190,7 @@
         <v>44834</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>44968</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>45873</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44968</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>46162</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>45877</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>46162</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>46162</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>45443</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>46161</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45960</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>45878</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>45972</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45877</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>45736</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45960</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>45970</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>45443</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>45314</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>45880</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>45475</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>45880</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40801,7 +40801,7 @@
         <v>45589</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>45880</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>46171</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>46170</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41103,7 +41103,7 @@
         <v>46173</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41176,7 +41176,7 @@
         <v>45882</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>45031</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>46173</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>45882</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>45882</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>46181</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>46181</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41702,7 +41702,7 @@
         <v>46181</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41775,7 +41775,7 @@
         <v>45970</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>46177</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41921,7 +41921,7 @@
         <v>45270</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41994,7 +41994,7 @@
         <v>45631</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42067,7 +42067,7 @@
         <v>46181</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42140,7 +42140,7 @@
         <v>46181</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>46181</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>46182</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>46181</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42437,7 +42437,7 @@
         <v>46181</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42515,7 +42515,7 @@
         <v>46183</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>46185</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>46185</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>46185</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>46185</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>46185</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42978,7 +42978,7 @@
         <v>45210</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43051,7 +43051,7 @@
         <v>46185</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43129,7 +43129,7 @@
         <v>44837</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>46185</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>46185</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43358,7 +43358,7 @@
         <v>44552</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43436,7 +43436,7 @@
         <v>46190</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43509,7 +43509,7 @@
         <v>44908</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43582,7 +43582,7 @@
         <v>45440</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43655,7 +43655,7 @@
         <v>46190</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43728,7 +43728,7 @@
         <v>46190</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43801,7 +43801,7 @@
         <v>44889</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>45597</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43952,7 +43952,7 @@
         <v>45611</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45523</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>46195</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>46195</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44254,7 +44254,7 @@
         <v>46195</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
         <v>45064</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>44841</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>46198</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44556,7 +44556,7 @@
         <v>46199</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44629,7 +44629,7 @@
         <v>45271</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>46199</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44780,7 +44780,7 @@
         <v>45630</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44853,7 +44853,7 @@
         <v>46199</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>46204</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45004,7 +45004,7 @@
         <v>46203</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>46204</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45160,7 +45160,7 @@
         <v>46146</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45233,7 +45233,7 @@
         <v>46206</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45311,7 +45311,7 @@
         <v>45463</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>46206</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45467,7 +45467,7 @@
         <v>46206</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45545,7 +45545,7 @@
         <v>45163</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45623,7 +45623,7 @@
         <v>46167</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45701,7 +45701,7 @@
         <v>46210</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>46210</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>46209</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         <v>45391</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>46178</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>46209</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46164,7 +46164,7 @@
         <v>46212</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46242,7 +46242,7 @@
         <v>46212</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46320,7 +46320,7 @@
         <v>46212</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46398,7 +46398,7 @@
         <v>46212</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>46212</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46554,7 +46554,7 @@
         <v>45541</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46632,7 +46632,7 @@
         <v>46214</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46705,7 +46705,7 @@
         <v>46157</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46783,7 +46783,7 @@
         <v>45884</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46861,7 +46861,7 @@
         <v>46258</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46939,7 +46939,7 @@
         <v>44970</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47012,7 +47012,7 @@
         <v>46204</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>46157</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>44860</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47241,7 +47241,7 @@
         <v>45131</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>46258</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47392,7 +47392,7 @@
         <v>45831</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47470,7 +47470,7 @@
         <v>46258</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>46258</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47626,7 +47626,7 @@
         <v>46258</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47704,7 +47704,7 @@
         <v>46148</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>45957</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47860,7 +47860,7 @@
         <v>46258</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47938,7 +47938,7 @@
         <v>46258</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>46261</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48094,7 +48094,7 @@
         <v>45548</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48167,7 +48167,7 @@
         <v>46265</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48240,7 +48240,7 @@
         <v>45558</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>44958</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48386,7 +48386,7 @@
         <v>46265</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48459,7 +48459,7 @@
         <v>46265</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>46265</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45418</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45012</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>46266</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48824,7 +48824,7 @@
         <v>46223</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>46223</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>44973</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49043,7 +49043,7 @@
         <v>45450</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49121,7 +49121,7 @@
         <v>46223</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49194,7 +49194,7 @@
         <v>46223</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>46223</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49340,7 +49340,7 @@
         <v>44691</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>46267</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>46266</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49564,7 +49564,7 @@
         <v>46225</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49642,7 +49642,7 @@
         <v>46225</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>46225</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>46225</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49876,7 +49876,7 @@
         <v>46225</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>46225</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50032,7 +50032,7 @@
         <v>46226</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50105,7 +50105,7 @@
         <v>46273</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>46227</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>46273</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50329,7 +50329,7 @@
         <v>46134</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50402,7 +50402,7 @@
         <v>46273</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50475,7 +50475,7 @@
         <v>46231</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50548,7 +50548,7 @@
         <v>46274</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>46274</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50699,7 +50699,7 @@
         <v>46274</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50772,7 +50772,7 @@
         <v>46198</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50845,7 +50845,7 @@
         <v>46274</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50918,7 +50918,7 @@
         <v>46275</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50996,7 +50996,7 @@
         <v>46279</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>46279</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51142,7 +51142,7 @@
         <v>46237</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>46234</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>46237</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51361,7 +51361,7 @@
         <v>46234</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51434,7 +51434,7 @@
         <v>46234</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51507,7 +51507,7 @@
         <v>46276</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51580,7 +51580,7 @@
         <v>46274</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51653,7 +51653,7 @@
         <v>45360</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51726,7 +51726,7 @@
         <v>46281</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>46265</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>45665</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51950,7 +51950,7 @@
         <v>46274</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52023,7 +52023,7 @@
         <v>46280</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52096,7 +52096,7 @@
         <v>46274</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>46280</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45307</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>46280</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52393,7 +52393,7 @@
         <v>45247</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>46280</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52544,7 +52544,7 @@
         <v>46280</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52622,7 +52622,7 @@
         <v>46280</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52700,7 +52700,7 @@
         <v>44854</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>46240</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>45613</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52924,7 +52924,7 @@
         <v>44944</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52997,7 +52997,7 @@
         <v>46241</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53070,7 +53070,7 @@
         <v>46240</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>45114</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45586</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53289,7 +53289,7 @@
         <v>46239</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53367,7 +53367,7 @@
         <v>45212</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53440,7 +53440,7 @@
         <v>46206</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53513,7 +53513,7 @@
         <v>46282</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>46284</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53664,7 +53664,7 @@
         <v>45925</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53737,7 +53737,7 @@
         <v>45204</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53810,7 +53810,7 @@
         <v>45385</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53883,7 +53883,7 @@
         <v>45974</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53956,7 +53956,7 @@
         <v>45356</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54029,7 +54029,7 @@
         <v>46243</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54102,7 +54102,7 @@
         <v>44641</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54175,7 +54175,7 @@
         <v>46244</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54248,7 +54248,7 @@
         <v>45611</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54321,7 +54321,7 @@
         <v>45062</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45356</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54467,7 +54467,7 @@
         <v>45407</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>45407</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54613,7 +54613,7 @@
         <v>44615</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>45930</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54759,7 +54759,7 @@
         <v>46241</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54837,7 +54837,7 @@
         <v>44568</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54910,7 +54910,7 @@
         <v>46286</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54988,7 +54988,7 @@
         <v>46244</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55061,7 +55061,7 @@
         <v>46246</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55134,7 +55134,7 @@
         <v>45196</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55207,7 +55207,7 @@
         <v>46245</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55285,7 +55285,7 @@
         <v>46246</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55358,7 +55358,7 @@
         <v>46246</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55431,7 +55431,7 @@
         <v>46245</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55509,7 +55509,7 @@
         <v>46288</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55587,7 +55587,7 @@
         <v>46245</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55665,7 +55665,7 @@
         <v>46246</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55738,7 +55738,7 @@
         <v>45488</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55816,7 +55816,7 @@
         <v>46246</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55889,7 +55889,7 @@
         <v>46289</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55967,7 +55967,7 @@
         <v>45523</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56040,7 +56040,7 @@
         <v>45523</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56113,7 +56113,7 @@
         <v>45777</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56186,7 +56186,7 @@
         <v>46248</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56264,7 +56264,7 @@
         <v>45372</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>46146</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56415,7 +56415,7 @@
         <v>46247</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56493,7 +56493,7 @@
         <v>45210</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56566,7 +56566,7 @@
         <v>46246</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56639,7 +56639,7 @@
         <v>46248</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56717,7 +56717,7 @@
         <v>45607</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45707</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>46252</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56936,7 +56936,7 @@
         <v>46252</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57014,7 +57014,7 @@
         <v>46290</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57087,7 +57087,7 @@
         <v>45278</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57160,7 +57160,7 @@
         <v>45602</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57233,7 +57233,7 @@
         <v>46290</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57306,7 +57306,7 @@
         <v>46290</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57379,7 +57379,7 @@
         <v>45370</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57452,7 +57452,7 @@
         <v>46251</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57530,7 +57530,7 @@
         <v>45265</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57603,7 +57603,7 @@
         <v>46252</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57676,7 +57676,7 @@
         <v>46251</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57754,7 +57754,7 @@
         <v>45216</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57827,7 +57827,7 @@
         <v>46290</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57900,7 +57900,7 @@
         <v>46290</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57973,7 +57973,7 @@
         <v>45258</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58046,7 +58046,7 @@
         <v>45407</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58119,7 +58119,7 @@
         <v>44574</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58192,7 +58192,7 @@
         <v>46251</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58270,7 +58270,7 @@
         <v>46132</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58343,7 +58343,7 @@
         <v>45603</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58421,7 +58421,7 @@
         <v>44923</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58494,7 +58494,7 @@
         <v>45210</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58567,7 +58567,7 @@
         <v>45709</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58640,7 +58640,7 @@
         <v>45770</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58713,7 +58713,7 @@
         <v>45968</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58786,7 +58786,7 @@
         <v>44988</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58859,7 +58859,7 @@
         <v>46254</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58937,7 +58937,7 @@
         <v>46253</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59015,7 +59015,7 @@
         <v>46254</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59093,7 +59093,7 @@
         <v>46251</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59166,7 +59166,7 @@
         <v>45371</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59244,7 +59244,7 @@
         <v>45427</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45671</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59390,7 +59390,7 @@
         <v>45631</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45136</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59536,7 +59536,7 @@
         <v>45475</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59609,7 +59609,7 @@
         <v>44988</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59682,7 +59682,7 @@
         <v>45309</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59760,7 +59760,7 @@
         <v>45309</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59838,7 +59838,7 @@
         <v>45630</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59911,7 +59911,7 @@
         <v>44832</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59984,7 +59984,7 @@
         <v>45583</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60062,7 +60062,7 @@
         <v>44959</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60135,7 +60135,7 @@
         <v>44743</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60208,7 +60208,7 @@
         <v>44892</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         <v>44959</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60359,7 +60359,7 @@
         <v>45463</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60437,7 +60437,7 @@
         <v>45491</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60510,7 +60510,7 @@
         <v>45621</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60583,7 +60583,7 @@
         <v>45418</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60656,7 +60656,7 @@
         <v>45585</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>44968</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60802,7 +60802,7 @@
         <v>45251</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60875,7 +60875,7 @@
         <v>45583</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60953,7 +60953,7 @@
         <v>45566</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61026,7 +61026,7 @@
         <v>44824</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61099,7 +61099,7 @@
         <v>45736</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61172,7 +61172,7 @@
         <v>45630</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61245,7 +61245,7 @@
         <v>45162</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61318,7 +61318,7 @@
         <v>45592</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61391,7 +61391,7 @@
         <v>45033</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61464,7 +61464,7 @@
         <v>45236</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61537,7 +61537,7 @@
         <v>45558</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61610,7 +61610,7 @@
         <v>45782</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61683,7 +61683,7 @@
         <v>45780</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61756,7 +61756,7 @@
         <v>45461</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61834,7 +61834,7 @@
         <v>45393</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61912,7 +61912,7 @@
         <v>44579</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61985,7 +61985,7 @@
         <v>44741</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62058,7 +62058,7 @@
         <v>44960</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62136,7 +62136,7 @@
         <v>44691</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62209,7 +62209,7 @@
         <v>44958</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62282,7 +62282,7 @@
         <v>44578</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62355,7 +62355,7 @@
         <v>44578</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62428,7 +62428,7 @@
         <v>44691</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62501,7 +62501,7 @@
         <v>45729</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62579,7 +62579,7 @@
         <v>45782</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62657,7 +62657,7 @@
         <v>45821</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62735,7 +62735,7 @@
         <v>45821</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62813,7 +62813,7 @@
         <v>45796</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62886,7 +62886,7 @@
         <v>45841</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62964,7 +62964,7 @@
         <v>46125</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63042,7 +63042,7 @@
         <v>46125</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63120,7 +63120,7 @@
         <v>46129</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63198,7 +63198,7 @@
         <v>46135</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63271,7 +63271,7 @@
         <v>46135</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63344,7 +63344,7 @@
         <v>46135</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63417,7 +63417,7 @@
         <v>46174</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63490,7 +63490,7 @@
         <v>46176</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63563,7 +63563,7 @@
         <v>46252</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>

--- a/Översikt PAJALA.xlsx
+++ b/Översikt PAJALA.xlsx
@@ -601,7 +601,7 @@
         <v>45880</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>44874</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>45749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45345</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>44503</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>46197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45407</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>45845</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>44608</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>45306</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>46171</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>44588</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>45405</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>45981</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>44608</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>46258</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>46260</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>44487</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>44608</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44874</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>44608</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>44893</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>45964</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>45841</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>46211</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>44608</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>46291</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>45671</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44943</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44503</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>46029</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>45902</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>46182</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>46182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>46212</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>46254</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>45469</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>45499</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>46052</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>45959</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>45957</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45530</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44760</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>44755</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44513</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>45392</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45643</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>44608</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>45973</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>44945</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>45476</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>46237</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>44895</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>45530</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45196</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>45769</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>44771</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45897</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>46034</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>45150</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>45902</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>46107</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>44930</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>46178</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>45163</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>46182</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>45755</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>46196</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>46204</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>46178</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>46258</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>46216</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>45215</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>44964</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>46225</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>46273</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>46274</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>46275</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>46237</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>44496</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>44608</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>45356</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>45791</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>45894</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>45894</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>46035</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>45938</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>45575</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>45585</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>45820</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>45722</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>46125</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>46128</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>45832</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>45838</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>45254</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>45611</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>45497</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>46153</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>45875</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>46188</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>46189</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>46189</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>45585</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>46204</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>46196</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>46227</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>46276</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>44854</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>44854</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>45121</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>46251</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>45216</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>44579</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>45394</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>46080</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>44755</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>44532</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>44691</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>44476</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
         <v>44691</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>44755</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>44755</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>44755</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>44602</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>44523</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>44691</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>44691</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>44691</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>44496</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44700</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>44756</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>44622</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15241,7 +15241,7 @@
         <v>44837</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>44884</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>44879</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>44627</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>44642</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>44875</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>44691</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>44629</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>44634</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15908,7 +15908,7 @@
         <v>44592</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>44663</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>44869</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>44627</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16200,7 +16200,7 @@
         <v>44873</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>44873</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>44518</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>44834</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>44663</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>44550</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>44552</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>44796</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>44749</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>44663</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>44521</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>44860</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>44862</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>44627</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>44691</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>45575</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>45467</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>45613</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>45275</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45698</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>45611</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>44804</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>44874</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>45454</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17972,7 +17972,7 @@
         <v>44504</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45238</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>45238</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         <v>45523</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>45006</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>44608</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>45611</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45002</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>46002</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>45884</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>46002</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>46002</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>45217</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>46002</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>46002</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>46002</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>46006</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>46006</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>46006</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>44960</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>44960</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>45054</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>44522</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>45477</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>46020</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>46021</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>46021</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>46020</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>45540</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20144,7 +20144,7 @@
         <v>45895</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>45665</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>45894</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>46029</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>46029</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>46029</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>46029</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>46029</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>45897</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20826,7 +20826,7 @@
         <v>45573</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>46031</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>46031</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>46030</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>45899</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>45898</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>45475</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>45898</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         <v>44756</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>46034</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>45902</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         <v>44874</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45902</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>45566</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>44892</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21946,7 +21946,7 @@
         <v>44517</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22019,7 +22019,7 @@
         <v>45905</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>46038</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>45906</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>45909</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>45909</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45794</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45796</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>45914</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>45169</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>44910</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22769,7 +22769,7 @@
         <v>46049</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>46048</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>45486</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>46049</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45201</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>45187</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>45918</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>45801</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>45919</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23441,7 +23441,7 @@
         <v>45919</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>45918</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>44860</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>45601</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45923</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>45592</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45807</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>45923</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45922</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45919</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>46052</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>45925</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>45925</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>45926</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>46059</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>46059</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45455</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>46059</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>46058</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>46059</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>46063</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>45678</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>45667</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>45469</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>46064</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>46065</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>46065</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>45936</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>45934</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45936</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>45936</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45936</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>45936</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>45938</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45938</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>45938</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>45671</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>45938</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26260,7 +26260,7 @@
         <v>45938</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>45227</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44477</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>45870</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>46072</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45939</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>45943</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45943</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45334</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>45944</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>46078</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>46077</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>45180</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44791</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>46078</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45952</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>45989</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>46080</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
         <v>45712</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27657,7 +27657,7 @@
         <v>46080</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>46080</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27803,7 +27803,7 @@
         <v>45477</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>46083</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>46083</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>45002</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         <v>46083</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>45505</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>45944</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>45399</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>46090</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>45965</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>45964</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28631,7 +28631,7 @@
         <v>45964</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>45154</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>45736</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>45334</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>45970</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>45583</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>45968</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>45971</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>45968</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>45972</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>45972</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>45227</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>44884</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>45972</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>45972</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>45972</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29809,7 +29809,7 @@
         <v>45972</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>45972</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>45972</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>45972</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>45972</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>45972</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30247,7 +30247,7 @@
         <v>45972</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30320,7 +30320,7 @@
         <v>45482</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>45975</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30466,7 +30466,7 @@
         <v>45447</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>46106</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30612,7 +30612,7 @@
         <v>46108</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30685,7 +30685,7 @@
         <v>45981</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>45981</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>45981</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>45631</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>45980</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>46108</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>46108</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>45387</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>45821</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>45820</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>45820</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>44894</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>45820</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>44916</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>45472</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>45820</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>45472</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>45764</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>44960</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>46113</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44547</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>45660</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45660</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>45988</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>45481</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>44568</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>45215</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>45557</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45827</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45740</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45995</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32983,7 +32983,7 @@
         <v>46125</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>46127</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45579</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>45579</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>46128</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33353,7 +33353,7 @@
         <v>45177</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>46132</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>46133</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>44973</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>46133</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33718,7 +33718,7 @@
         <v>46132</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
         <v>46131</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33864,7 +33864,7 @@
         <v>46133</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45474</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>45477</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>46133</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34156,7 +34156,7 @@
         <v>46135</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34229,7 +34229,7 @@
         <v>45832</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>46135</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>46135</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
         <v>46135</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34526,7 +34526,7 @@
         <v>46135</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34599,7 +34599,7 @@
         <v>46135</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34672,7 +34672,7 @@
         <v>45491</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         <v>46135</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34818,7 +34818,7 @@
         <v>45316</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>45454</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>45434</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>45838</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>45599</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>45603</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35271,7 +35271,7 @@
         <v>46139</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35344,7 +35344,7 @@
         <v>45838</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35422,7 +35422,7 @@
         <v>45840</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35500,7 +35500,7 @@
         <v>45841</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35573,7 +35573,7 @@
         <v>45849</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>45297</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35724,7 +35724,7 @@
         <v>45849</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>46136</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44968</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35948,7 +35948,7 @@
         <v>45855</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>44518</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36099,7 +36099,7 @@
         <v>44578</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36172,7 +36172,7 @@
         <v>45498</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36245,7 +36245,7 @@
         <v>45406</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36318,7 +36318,7 @@
         <v>45012</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>46134</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>44892</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>46136</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>45856</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>44861</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>45624</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>45177</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36907,7 +36907,7 @@
         <v>45623</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36980,7 +36980,7 @@
         <v>45910</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37053,7 +37053,7 @@
         <v>45863</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37126,7 +37126,7 @@
         <v>45616</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37199,7 +37199,7 @@
         <v>45118</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>45586</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37345,7 +37345,7 @@
         <v>45586</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>45580</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>45058</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>45152</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>45560</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45868</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37788,7 +37788,7 @@
         <v>44790</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>45862</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>45427</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>45630</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45218</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>46147</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38236,7 +38236,7 @@
         <v>46146</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45873</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38382,7 +38382,7 @@
         <v>45136</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>44988</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45592</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45592</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38674,7 +38674,7 @@
         <v>45682</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38747,7 +38747,7 @@
         <v>45265</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>45247</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>44755</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38966,7 +38966,7 @@
         <v>46155</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>44778</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>44755</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39190,7 +39190,7 @@
         <v>44834</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>44968</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>45873</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44968</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>46162</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>45877</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>46162</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>46162</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>45443</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>46161</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45960</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>45878</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>45972</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45877</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>45736</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45960</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>45970</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>45443</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>45314</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>45880</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>45475</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>45880</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40801,7 +40801,7 @@
         <v>45589</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>45880</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>46171</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>46170</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41103,7 +41103,7 @@
         <v>46173</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41176,7 +41176,7 @@
         <v>45882</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>45031</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>46173</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>45882</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>45882</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>46181</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>46181</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41702,7 +41702,7 @@
         <v>46181</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41775,7 +41775,7 @@
         <v>45970</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>46177</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41921,7 +41921,7 @@
         <v>45270</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41994,7 +41994,7 @@
         <v>45631</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42067,7 +42067,7 @@
         <v>46181</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42140,7 +42140,7 @@
         <v>46181</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>46181</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>46182</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>46181</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42437,7 +42437,7 @@
         <v>46181</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42515,7 +42515,7 @@
         <v>46183</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>46185</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>46185</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>46185</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>46185</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>46185</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42978,7 +42978,7 @@
         <v>45210</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43051,7 +43051,7 @@
         <v>46185</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43129,7 +43129,7 @@
         <v>44837</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>46185</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>46185</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43358,7 +43358,7 @@
         <v>44552</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43436,7 +43436,7 @@
         <v>46190</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43509,7 +43509,7 @@
         <v>44908</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43582,7 +43582,7 @@
         <v>45440</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43655,7 +43655,7 @@
         <v>46190</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43728,7 +43728,7 @@
         <v>46190</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43801,7 +43801,7 @@
         <v>44889</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>45597</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43952,7 +43952,7 @@
         <v>45611</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45523</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>46195</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>46195</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44254,7 +44254,7 @@
         <v>46195</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
         <v>45064</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>44841</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>46198</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44556,7 +44556,7 @@
         <v>46199</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44629,7 +44629,7 @@
         <v>45271</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>46199</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44780,7 +44780,7 @@
         <v>45630</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44853,7 +44853,7 @@
         <v>46199</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>46204</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45004,7 +45004,7 @@
         <v>46203</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>46204</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45160,7 +45160,7 @@
         <v>46146</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45233,7 +45233,7 @@
         <v>46206</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45311,7 +45311,7 @@
         <v>45463</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>46206</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45467,7 +45467,7 @@
         <v>46206</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45545,7 +45545,7 @@
         <v>45163</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45623,7 +45623,7 @@
         <v>46167</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45701,7 +45701,7 @@
         <v>46210</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>46210</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>46209</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         <v>45391</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>46178</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>46209</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46164,7 +46164,7 @@
         <v>46212</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46242,7 +46242,7 @@
         <v>46212</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46320,7 +46320,7 @@
         <v>46212</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46398,7 +46398,7 @@
         <v>46212</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>46212</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46554,7 +46554,7 @@
         <v>45541</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46632,7 +46632,7 @@
         <v>46214</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46705,7 +46705,7 @@
         <v>46157</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46783,7 +46783,7 @@
         <v>45884</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46861,7 +46861,7 @@
         <v>46258</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46939,7 +46939,7 @@
         <v>44970</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47012,7 +47012,7 @@
         <v>46204</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>46157</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>44860</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47241,7 +47241,7 @@
         <v>45131</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>46258</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47392,7 +47392,7 @@
         <v>45831</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47470,7 +47470,7 @@
         <v>46258</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>46258</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47626,7 +47626,7 @@
         <v>46258</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47704,7 +47704,7 @@
         <v>46148</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>45957</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47860,7 +47860,7 @@
         <v>46258</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47938,7 +47938,7 @@
         <v>46258</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>46261</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48094,7 +48094,7 @@
         <v>45548</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48167,7 +48167,7 @@
         <v>46265</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48240,7 +48240,7 @@
         <v>45558</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>44958</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48386,7 +48386,7 @@
         <v>46265</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48459,7 +48459,7 @@
         <v>46265</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>46265</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45418</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45012</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>46266</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48824,7 +48824,7 @@
         <v>46223</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>46223</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>44973</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49043,7 +49043,7 @@
         <v>45450</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49121,7 +49121,7 @@
         <v>46223</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49194,7 +49194,7 @@
         <v>46223</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>46223</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49340,7 +49340,7 @@
         <v>44691</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>46267</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>46266</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49564,7 +49564,7 @@
         <v>46225</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49642,7 +49642,7 @@
         <v>46225</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>46225</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>46225</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49876,7 +49876,7 @@
         <v>46225</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>46225</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50032,7 +50032,7 @@
         <v>46226</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50105,7 +50105,7 @@
         <v>46273</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>46227</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>46273</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50329,7 +50329,7 @@
         <v>46134</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50402,7 +50402,7 @@
         <v>46273</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50475,7 +50475,7 @@
         <v>46231</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50548,7 +50548,7 @@
         <v>46274</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>46274</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50699,7 +50699,7 @@
         <v>46274</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50772,7 +50772,7 @@
         <v>46198</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50845,7 +50845,7 @@
         <v>46274</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50918,7 +50918,7 @@
         <v>46275</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50996,7 +50996,7 @@
         <v>46279</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>46279</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51142,7 +51142,7 @@
         <v>46237</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>46234</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>46237</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51361,7 +51361,7 @@
         <v>46234</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51434,7 +51434,7 @@
         <v>46234</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51507,7 +51507,7 @@
         <v>46276</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51580,7 +51580,7 @@
         <v>46274</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51653,7 +51653,7 @@
         <v>45360</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51726,7 +51726,7 @@
         <v>46281</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>46265</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>45665</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51950,7 +51950,7 @@
         <v>46274</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52023,7 +52023,7 @@
         <v>46280</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52096,7 +52096,7 @@
         <v>46274</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>46280</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45307</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>46280</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52393,7 +52393,7 @@
         <v>45247</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>46280</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52544,7 +52544,7 @@
         <v>46280</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52622,7 +52622,7 @@
         <v>46280</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52700,7 +52700,7 @@
         <v>44854</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>46240</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>45613</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52924,7 +52924,7 @@
         <v>44944</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52997,7 +52997,7 @@
         <v>46241</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53070,7 +53070,7 @@
         <v>46240</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>45114</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45586</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53289,7 +53289,7 @@
         <v>46239</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53367,7 +53367,7 @@
         <v>45212</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53440,7 +53440,7 @@
         <v>46206</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53513,7 +53513,7 @@
         <v>46282</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>46284</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53664,7 +53664,7 @@
         <v>45925</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53737,7 +53737,7 @@
         <v>45204</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53810,7 +53810,7 @@
         <v>45385</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53883,7 +53883,7 @@
         <v>45974</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53956,7 +53956,7 @@
         <v>45356</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54029,7 +54029,7 @@
         <v>46243</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54102,7 +54102,7 @@
         <v>44641</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54175,7 +54175,7 @@
         <v>46244</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54248,7 +54248,7 @@
         <v>45611</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54321,7 +54321,7 @@
         <v>45062</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45356</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54467,7 +54467,7 @@
         <v>45407</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>45407</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54613,7 +54613,7 @@
         <v>44615</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>45930</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54759,7 +54759,7 @@
         <v>46241</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54837,7 +54837,7 @@
         <v>44568</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54910,7 +54910,7 @@
         <v>46286</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54988,7 +54988,7 @@
         <v>46244</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55061,7 +55061,7 @@
         <v>46246</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55134,7 +55134,7 @@
         <v>45196</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55207,7 +55207,7 @@
         <v>46245</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55285,7 +55285,7 @@
         <v>46246</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55358,7 +55358,7 @@
         <v>46246</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55431,7 +55431,7 @@
         <v>46245</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55509,7 +55509,7 @@
         <v>46288</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55587,7 +55587,7 @@
         <v>46245</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55665,7 +55665,7 @@
         <v>46246</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55738,7 +55738,7 @@
         <v>45488</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55816,7 +55816,7 @@
         <v>46246</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55889,7 +55889,7 @@
         <v>46289</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55967,7 +55967,7 @@
         <v>45523</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56040,7 +56040,7 @@
         <v>45523</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56113,7 +56113,7 @@
         <v>45777</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56186,7 +56186,7 @@
         <v>46248</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56264,7 +56264,7 @@
         <v>45372</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>46146</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56415,7 +56415,7 @@
         <v>46247</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56493,7 +56493,7 @@
         <v>45210</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56566,7 +56566,7 @@
         <v>46246</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56639,7 +56639,7 @@
         <v>46248</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56717,7 +56717,7 @@
         <v>45607</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45707</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>46252</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56936,7 +56936,7 @@
         <v>46252</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57014,7 +57014,7 @@
         <v>46290</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57087,7 +57087,7 @@
         <v>45278</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57160,7 +57160,7 @@
         <v>45602</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57233,7 +57233,7 @@
         <v>46290</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57306,7 +57306,7 @@
         <v>46290</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57379,7 +57379,7 @@
         <v>45370</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57452,7 +57452,7 @@
         <v>46251</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57530,7 +57530,7 @@
         <v>45265</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57603,7 +57603,7 @@
         <v>46252</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57676,7 +57676,7 @@
         <v>46251</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57754,7 +57754,7 @@
         <v>45216</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57827,7 +57827,7 @@
         <v>46290</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57900,7 +57900,7 @@
         <v>46290</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57973,7 +57973,7 @@
         <v>45258</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58046,7 +58046,7 @@
         <v>45407</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58119,7 +58119,7 @@
         <v>44574</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58192,7 +58192,7 @@
         <v>46251</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58270,7 +58270,7 @@
         <v>46132</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58343,7 +58343,7 @@
         <v>45603</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58421,7 +58421,7 @@
         <v>44923</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58494,7 +58494,7 @@
         <v>45210</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58567,7 +58567,7 @@
         <v>45709</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58640,7 +58640,7 @@
         <v>45770</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58713,7 +58713,7 @@
         <v>45968</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58786,7 +58786,7 @@
         <v>44988</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58859,7 +58859,7 @@
         <v>46254</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58937,7 +58937,7 @@
         <v>46253</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59015,7 +59015,7 @@
         <v>46254</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59093,7 +59093,7 @@
         <v>46251</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59166,7 +59166,7 @@
         <v>45371</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59244,7 +59244,7 @@
         <v>45427</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45671</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59390,7 +59390,7 @@
         <v>45631</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45136</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59536,7 +59536,7 @@
         <v>45475</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59609,7 +59609,7 @@
         <v>44988</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59682,7 +59682,7 @@
         <v>45309</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59760,7 +59760,7 @@
         <v>45309</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59838,7 +59838,7 @@
         <v>45630</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59911,7 +59911,7 @@
         <v>44832</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59984,7 +59984,7 @@
         <v>45583</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60062,7 +60062,7 @@
         <v>44959</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60135,7 +60135,7 @@
         <v>44743</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60208,7 +60208,7 @@
         <v>44892</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         <v>44959</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60359,7 +60359,7 @@
         <v>45463</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60437,7 +60437,7 @@
         <v>45491</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60510,7 +60510,7 @@
         <v>45621</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60583,7 +60583,7 @@
         <v>45418</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60656,7 +60656,7 @@
         <v>45585</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>44968</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60802,7 +60802,7 @@
         <v>45251</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60875,7 +60875,7 @@
         <v>45583</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60953,7 +60953,7 @@
         <v>45566</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61026,7 +61026,7 @@
         <v>44824</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61099,7 +61099,7 @@
         <v>45736</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61172,7 +61172,7 @@
         <v>45630</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61245,7 +61245,7 @@
         <v>45162</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61318,7 +61318,7 @@
         <v>45592</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61391,7 +61391,7 @@
         <v>45033</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61464,7 +61464,7 @@
         <v>45236</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61537,7 +61537,7 @@
         <v>45558</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61610,7 +61610,7 @@
         <v>45782</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61683,7 +61683,7 @@
         <v>45780</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61756,7 +61756,7 @@
         <v>45461</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61834,7 +61834,7 @@
         <v>45393</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61912,7 +61912,7 @@
         <v>44579</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61985,7 +61985,7 @@
         <v>44741</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62058,7 +62058,7 @@
         <v>44960</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62136,7 +62136,7 @@
         <v>44691</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62209,7 +62209,7 @@
         <v>44958</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62282,7 +62282,7 @@
         <v>44578</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62355,7 +62355,7 @@
         <v>44578</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62428,7 +62428,7 @@
         <v>44691</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62501,7 +62501,7 @@
         <v>45729</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62579,7 +62579,7 @@
         <v>45782</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62657,7 +62657,7 @@
         <v>45821</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62735,7 +62735,7 @@
         <v>45821</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62813,7 +62813,7 @@
         <v>45796</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62886,7 +62886,7 @@
         <v>45841</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62964,7 +62964,7 @@
         <v>46125</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63042,7 +63042,7 @@
         <v>46125</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63120,7 +63120,7 @@
         <v>46129</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63198,7 +63198,7 @@
         <v>46135</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63271,7 +63271,7 @@
         <v>46135</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63344,7 +63344,7 @@
         <v>46135</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63417,7 +63417,7 @@
         <v>46174</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63490,7 +63490,7 @@
         <v>46176</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63563,7 +63563,7 @@
         <v>46252</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>

--- a/Översikt PAJALA.xlsx
+++ b/Översikt PAJALA.xlsx
@@ -601,7 +601,7 @@
         <v>45880</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>44874</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>45749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45345</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>44503</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>46197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45407</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>45845</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>44608</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>45306</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>46171</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>44588</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>44608</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45981</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>45405</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>46258</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>46260</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>44487</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>44874</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44608</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>44608</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>44893</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>44608</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>45964</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>45841</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>46211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>46291</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>45671</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44943</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44503</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45902</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>46029</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>46182</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>46182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>46212</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>46254</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>45469</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>45499</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>45959</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>45530</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>46052</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>45957</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44760</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>44755</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>46300</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44513</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45643</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>44608</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>45196</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>44945</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>45392</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>45973</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>44895</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>45530</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>45769</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>45476</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>46237</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>45215</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44771</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>45163</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>45897</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>45902</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>45755</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>45150</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44930</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>46107</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>44964</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>46034</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>46178</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>46182</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>46196</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>46204</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>46178</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>46216</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>46225</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>46274</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>46273</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>46275</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>46237</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>46258</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>46302</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>44496</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>45254</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>45216</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>44854</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>44854</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>45894</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>45894</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45497</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>45611</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>45585</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>45585</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>45791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>45356</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>45575</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>44608</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>45938</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>45820</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12048,7 +12048,7 @@
         <v>45832</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>45838</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>45875</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>45722</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>46125</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>46128</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>46035</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>45121</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         <v>46153</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>46188</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>46189</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>46189</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>46204</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>46196</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>46227</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>46276</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>46251</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>44579</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
         <v>45394</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>46080</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>44691</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44755</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>44691</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>44532</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>44755</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>44755</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>44755</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>44602</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44523</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>44691</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>44691</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>44691</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>44496</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>44700</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>44756</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>44622</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>44837</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>44879</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>44884</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44627</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>44642</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>44875</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>44552</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>44873</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>44873</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>44796</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>44521</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>44691</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44629</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>44518</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>44634</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>44592</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>44663</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>44860</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>44749</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>44834</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>44869</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44663</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>44663</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>44862</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>44627</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>44550</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44892</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>44627</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>44691</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>45467</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45434</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>45210</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45391</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>45334</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44743</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>45275</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>45215</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>45334</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>44892</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45270</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>45630</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>45613</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>45012</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>45309</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45592</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45307</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45450</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>45360</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>44960</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>45611</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>44574</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>45477</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>44968</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>45418</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45454</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>44568</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>44517</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>45371</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>45218</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>45770</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>45882</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>45204</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         <v>45201</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45463</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         <v>45884</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>45118</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>45611</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20351,7 +20351,7 @@
         <v>45169</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>44854</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>45247</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20580,7 +20580,7 @@
         <v>45278</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>45474</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>45463</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>45271</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>44894</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>45265</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
         <v>45671</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>45154</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>45573</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>45580</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>45297</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>44790</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>45682</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>44970</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>45477</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>45455</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>45314</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>45498</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21904,7 +21904,7 @@
         <v>44908</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>44944</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>44892</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>45491</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>45469</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>44837</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>45427</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>45894</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>45895</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>45898</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>45897</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>45898</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>44889</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>45385</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>45603</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>45902</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>44973</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>45624</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45601</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>45899</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>45227</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>45902</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>44884</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23618,7 +23618,7 @@
         <v>45033</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>45665</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>45427</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>45505</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>45906</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>45114</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>45905</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>44874</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>45621</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>45603</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>45523</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>45909</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24504,7 +24504,7 @@
         <v>45597</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>45475</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>45909</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>45236</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45611</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45454</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>45566</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>45780</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>45782</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>45558</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>44988</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>45914</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>45560</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>45002</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>45557</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>45678</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>45918</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>45918</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25838,7 +25838,7 @@
         <v>45447</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>45592</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>45592</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>45922</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>45919</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>45919</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>45919</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>45418</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>45006</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>45923</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>44959</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>45486</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>45923</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>45217</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45613</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45926</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27031,7 +27031,7 @@
         <v>45925</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>45481</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27177,7 +27177,7 @@
         <v>45589</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
         <v>45925</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>45630</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44568</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>45796</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>45794</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>45631</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>44641</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>45488</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>45586</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>45585</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>44552</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>45491</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>45058</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>45579</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>45579</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>45936</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>45934</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>45660</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>45660</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>44578</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>45936</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>45936</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44923</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>45936</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29017,7 +29017,7 @@
         <v>45407</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>45407</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>45936</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>45064</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>45801</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>45764</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>44755</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>45372</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44860</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>45177</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>44973</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>45938</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>44959</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>45807</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>45671</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30137,7 +30137,7 @@
         <v>44791</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>45870</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>45667</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>45558</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>45251</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>44988</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30580,7 +30580,7 @@
         <v>45002</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>45938</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30731,7 +30731,7 @@
         <v>45939</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30804,7 +30804,7 @@
         <v>45938</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>45938</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>45938</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31023,7 +31023,7 @@
         <v>45943</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31096,7 +31096,7 @@
         <v>45944</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>45399</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31242,7 +31242,7 @@
         <v>45407</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>45712</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45943</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>44691</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>44968</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>45736</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>45131</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>45820</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>45820</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>44874</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>45820</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>45623</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>45820</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>45821</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>45472</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>45630</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>45472</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>45583</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45177</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45583</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>45827</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>44615</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>44860</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>45523</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>45709</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>45583</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>45387</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33253,7 +33253,7 @@
         <v>45832</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33331,7 +33331,7 @@
         <v>45136</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>45944</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33477,7 +33477,7 @@
         <v>45631</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33550,7 +33550,7 @@
         <v>45964</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>45187</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33696,7 +33696,7 @@
         <v>45964</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>45838</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33847,7 +33847,7 @@
         <v>45630</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>45838</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33998,7 +33998,7 @@
         <v>44832</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34071,7 +34071,7 @@
         <v>45840</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34149,7 +34149,7 @@
         <v>45965</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34222,7 +34222,7 @@
         <v>45841</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>45968</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>45631</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>45210</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>45968</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34587,7 +34587,7 @@
         <v>45972</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34660,7 +34660,7 @@
         <v>45972</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34733,7 +34733,7 @@
         <v>45972</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34806,7 +34806,7 @@
         <v>45665</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>45970</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>45972</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35025,7 +35025,7 @@
         <v>45972</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>45972</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>44841</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35244,7 +35244,7 @@
         <v>45972</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35317,7 +35317,7 @@
         <v>45972</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35390,7 +35390,7 @@
         <v>45972</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>45972</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35536,7 +35536,7 @@
         <v>45971</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35614,7 +35614,7 @@
         <v>45972</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35687,7 +35687,7 @@
         <v>45972</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>45849</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35838,7 +35838,7 @@
         <v>45849</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>44778</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45736</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>45196</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>45592</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>45856</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>44756</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>45855</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36432,7 +36432,7 @@
         <v>45316</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45309</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         <v>45227</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>44504</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>45440</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36802,7 +36802,7 @@
         <v>45863</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>45868</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>45975</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>44861</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>45980</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37182,7 +37182,7 @@
         <v>45443</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37260,7 +37260,7 @@
         <v>45477</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>45482</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>45873</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>45873</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>45210</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>45238</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>45238</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>45162</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>45877</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>45475</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45880</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38068,7 +38068,7 @@
         <v>45877</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38141,7 +38141,7 @@
         <v>44824</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38214,7 +38214,7 @@
         <v>45880</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38287,7 +38287,7 @@
         <v>45981</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38360,7 +38360,7 @@
         <v>44834</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>45880</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>45258</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>45882</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>45882</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>45212</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>45981</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38881,7 +38881,7 @@
         <v>45981</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>45698</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>45616</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>45136</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>44916</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>45247</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
         <v>45265</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>46106</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45523</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>45523</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39611,7 +39611,7 @@
         <v>46108</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39684,7 +39684,7 @@
         <v>45180</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>46108</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>45988</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>46108</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45054</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40049,7 +40049,7 @@
         <v>45406</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40122,7 +40122,7 @@
         <v>46113</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>45599</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>45540</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>44910</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>45740</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40492,7 +40492,7 @@
         <v>44518</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>46125</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>45995</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>44522</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>46002</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40867,7 +40867,7 @@
         <v>46127</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>46128</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>46132</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41091,7 +41091,7 @@
         <v>46002</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41169,7 +41169,7 @@
         <v>46132</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41242,7 +41242,7 @@
         <v>45566</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41315,7 +41315,7 @@
         <v>44804</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41388,7 +41388,7 @@
         <v>44988</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41461,7 +41461,7 @@
         <v>46002</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>46002</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>46131</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41690,7 +41690,7 @@
         <v>46002</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>46002</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41836,7 +41836,7 @@
         <v>46133</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41909,7 +41909,7 @@
         <v>46133</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>44960</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42060,7 +42060,7 @@
         <v>44960</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>45586</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>45586</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>46133</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>46006</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42430,7 +42430,7 @@
         <v>46133</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
         <v>46006</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>46006</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42649,7 +42649,7 @@
         <v>46134</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42722,7 +42722,7 @@
         <v>46135</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42795,7 +42795,7 @@
         <v>46135</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>46136</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>46135</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>46135</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>46135</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>46135</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43233,7 +43233,7 @@
         <v>46136</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43306,7 +43306,7 @@
         <v>45216</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43379,7 +43379,7 @@
         <v>44958</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>46135</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>45862</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>46020</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43676,7 +43676,7 @@
         <v>46020</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>46021</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43822,7 +43822,7 @@
         <v>46021</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>46139</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>44547</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>46029</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>46030</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45152</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>46029</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44338,7 +44338,7 @@
         <v>46029</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>46029</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44494,7 +44494,7 @@
         <v>46031</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44567,7 +44567,7 @@
         <v>46031</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>46034</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>45031</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44786,7 +44786,7 @@
         <v>46038</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45602</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>44608</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>46048</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45088,7 +45088,7 @@
         <v>45475</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45910</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>45575</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>46049</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45012</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45607</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>46049</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>46052</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45682,7 +45682,7 @@
         <v>46058</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>46059</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>46059</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>46059</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>46059</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>46146</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>46063</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>46065</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>46064</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>46147</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46417,7 +46417,7 @@
         <v>46065</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>46072</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>46077</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>44755</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46709,7 +46709,7 @@
         <v>46078</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46782,7 +46782,7 @@
         <v>45989</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46855,7 +46855,7 @@
         <v>45952</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>46078</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>46083</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>46083</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47157,7 +47157,7 @@
         <v>46083</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47235,7 +47235,7 @@
         <v>46080</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47308,7 +47308,7 @@
         <v>46080</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47381,7 +47381,7 @@
         <v>46080</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47454,7 +47454,7 @@
         <v>46155</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47532,7 +47532,7 @@
         <v>46090</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47610,7 +47610,7 @@
         <v>44968</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47683,7 +47683,7 @@
         <v>46162</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
         <v>44968</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47829,7 +47829,7 @@
         <v>46162</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>46162</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>45443</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48048,7 +48048,7 @@
         <v>46161</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48121,7 +48121,7 @@
         <v>45878</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>45960</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48267,7 +48267,7 @@
         <v>45970</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48340,7 +48340,7 @@
         <v>45972</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48413,7 +48413,7 @@
         <v>45960</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>45736</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48559,7 +48559,7 @@
         <v>46173</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>46173</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48705,7 +48705,7 @@
         <v>46171</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>46170</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>46177</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48929,7 +48929,7 @@
         <v>46181</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>46181</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49080,7 +49080,7 @@
         <v>46181</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45970</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>46182</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>46181</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>46181</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49450,7 +49450,7 @@
         <v>46181</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49523,7 +49523,7 @@
         <v>46181</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49596,7 +49596,7 @@
         <v>46181</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>46183</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>46185</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49820,7 +49820,7 @@
         <v>46185</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49898,7 +49898,7 @@
         <v>46185</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49976,7 +49976,7 @@
         <v>46185</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50054,7 +50054,7 @@
         <v>46185</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>46185</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50210,7 +50210,7 @@
         <v>46185</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50288,7 +50288,7 @@
         <v>46185</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50366,7 +50366,7 @@
         <v>46190</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>46190</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         <v>46190</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50585,7 +50585,7 @@
         <v>46195</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50663,7 +50663,7 @@
         <v>46195</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50741,7 +50741,7 @@
         <v>46195</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50819,7 +50819,7 @@
         <v>46199</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>46199</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50965,7 +50965,7 @@
         <v>46199</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51043,7 +51043,7 @@
         <v>46198</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51121,7 +51121,7 @@
         <v>46203</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51199,7 +51199,7 @@
         <v>46204</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51277,7 +51277,7 @@
         <v>46204</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51355,7 +51355,7 @@
         <v>46167</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>45163</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>46209</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         <v>46206</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>46206</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51745,7 +51745,7 @@
         <v>46209</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51823,7 +51823,7 @@
         <v>46146</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51896,7 +51896,7 @@
         <v>46206</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51974,7 +51974,7 @@
         <v>46210</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>46178</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52130,7 +52130,7 @@
         <v>46210</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>46212</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52286,7 +52286,7 @@
         <v>46212</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         <v>46157</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52442,7 +52442,7 @@
         <v>46204</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52520,7 +52520,7 @@
         <v>45541</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52598,7 +52598,7 @@
         <v>45957</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52676,7 +52676,7 @@
         <v>45831</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
         <v>46214</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52827,7 +52827,7 @@
         <v>46212</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52905,7 +52905,7 @@
         <v>46212</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52983,7 +52983,7 @@
         <v>46148</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53061,7 +53061,7 @@
         <v>46212</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53139,7 +53139,7 @@
         <v>46157</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53217,7 +53217,7 @@
         <v>45884</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53295,7 +53295,7 @@
         <v>45548</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53368,7 +53368,7 @@
         <v>46265</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53441,7 +53441,7 @@
         <v>46265</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53514,7 +53514,7 @@
         <v>46266</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53587,7 +53587,7 @@
         <v>46223</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53660,7 +53660,7 @@
         <v>46223</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53733,7 +53733,7 @@
         <v>46265</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53806,7 +53806,7 @@
         <v>46266</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53879,7 +53879,7 @@
         <v>46223</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53952,7 +53952,7 @@
         <v>46223</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54025,7 +54025,7 @@
         <v>46265</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54098,7 +54098,7 @@
         <v>46223</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54171,7 +54171,7 @@
         <v>46225</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54249,7 +54249,7 @@
         <v>46225</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54327,7 +54327,7 @@
         <v>46225</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54405,7 +54405,7 @@
         <v>46267</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>46225</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54561,7 +54561,7 @@
         <v>46225</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54639,7 +54639,7 @@
         <v>46225</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54717,7 +54717,7 @@
         <v>46227</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54790,7 +54790,7 @@
         <v>46134</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54863,7 +54863,7 @@
         <v>46226</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         <v>46273</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55014,7 +55014,7 @@
         <v>46274</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55092,7 +55092,7 @@
         <v>46274</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>46274</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55238,7 +55238,7 @@
         <v>46273</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55311,7 +55311,7 @@
         <v>46274</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55384,7 +55384,7 @@
         <v>46198</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55457,7 +55457,7 @@
         <v>46231</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55530,7 +55530,7 @@
         <v>46273</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55603,7 +55603,7 @@
         <v>46276</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55676,7 +55676,7 @@
         <v>46275</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55754,7 +55754,7 @@
         <v>46280</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55832,7 +55832,7 @@
         <v>46279</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55905,7 +55905,7 @@
         <v>46234</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55978,7 +55978,7 @@
         <v>46280</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56051,7 +56051,7 @@
         <v>46280</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56129,7 +56129,7 @@
         <v>46237</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56202,7 +56202,7 @@
         <v>46280</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56280,7 +56280,7 @@
         <v>46280</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56358,7 +56358,7 @@
         <v>46280</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56431,7 +56431,7 @@
         <v>46237</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         <v>46234</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>46279</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56650,7 +56650,7 @@
         <v>46234</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56723,7 +56723,7 @@
         <v>46274</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56796,7 +56796,7 @@
         <v>46240</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56869,7 +56869,7 @@
         <v>46282</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56947,7 +56947,7 @@
         <v>46239</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57025,7 +57025,7 @@
         <v>46265</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57098,7 +57098,7 @@
         <v>46274</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57171,7 +57171,7 @@
         <v>46240</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57244,7 +57244,7 @@
         <v>46281</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57322,7 +57322,7 @@
         <v>46206</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57395,7 +57395,7 @@
         <v>46274</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57468,7 +57468,7 @@
         <v>46286</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57546,7 +57546,7 @@
         <v>46241</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57624,7 +57624,7 @@
         <v>46243</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57697,7 +57697,7 @@
         <v>46241</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57770,7 +57770,7 @@
         <v>45974</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57843,7 +57843,7 @@
         <v>45611</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57916,7 +57916,7 @@
         <v>45062</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57989,7 +57989,7 @@
         <v>46244</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         <v>45925</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58135,7 +58135,7 @@
         <v>46245</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58213,7 +58213,7 @@
         <v>46288</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58291,7 +58291,7 @@
         <v>45930</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58364,7 +58364,7 @@
         <v>46245</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58442,7 +58442,7 @@
         <v>46284</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58515,7 +58515,7 @@
         <v>46244</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>46245</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58666,7 +58666,7 @@
         <v>46247</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58744,7 +58744,7 @@
         <v>45707</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58817,7 +58817,7 @@
         <v>46246</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58890,7 +58890,7 @@
         <v>46246</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58963,7 +58963,7 @@
         <v>46246</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59036,7 +59036,7 @@
         <v>46246</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59109,7 +59109,7 @@
         <v>46146</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59182,7 +59182,7 @@
         <v>46246</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59255,7 +59255,7 @@
         <v>46289</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59333,7 +59333,7 @@
         <v>45777</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>46248</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59484,7 +59484,7 @@
         <v>46290</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59557,7 +59557,7 @@
         <v>46248</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59635,7 +59635,7 @@
         <v>46290</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59708,7 +59708,7 @@
         <v>46290</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59781,7 +59781,7 @@
         <v>46290</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59854,7 +59854,7 @@
         <v>46246</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59927,7 +59927,7 @@
         <v>46252</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60000,7 +60000,7 @@
         <v>46290</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>46251</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60151,7 +60151,7 @@
         <v>46252</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         <v>46252</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60302,7 +60302,7 @@
         <v>46251</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60380,7 +60380,7 @@
         <v>46253</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60458,7 +60458,7 @@
         <v>45370</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60531,7 +60531,7 @@
         <v>46258</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60609,7 +60609,7 @@
         <v>46258</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60687,7 +60687,7 @@
         <v>46258</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60765,7 +60765,7 @@
         <v>46254</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60843,7 +60843,7 @@
         <v>46254</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60921,7 +60921,7 @@
         <v>46258</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60999,7 +60999,7 @@
         <v>46258</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61077,7 +61077,7 @@
         <v>46251</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61150,7 +61150,7 @@
         <v>45968</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61223,7 +61223,7 @@
         <v>46298</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61296,7 +61296,7 @@
         <v>46251</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61374,7 +61374,7 @@
         <v>46258</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61452,7 +61452,7 @@
         <v>46258</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61530,7 +61530,7 @@
         <v>46301</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61603,7 +61603,7 @@
         <v>46132</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61676,7 +61676,7 @@
         <v>46301</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61749,7 +61749,7 @@
         <v>45356</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61822,7 +61822,7 @@
         <v>45356</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61895,7 +61895,7 @@
         <v>46303</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61968,7 +61968,7 @@
         <v>46261</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62046,7 +62046,7 @@
         <v>44579</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62119,7 +62119,7 @@
         <v>44691</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62192,7 +62192,7 @@
         <v>44578</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62265,7 +62265,7 @@
         <v>44578</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62338,7 +62338,7 @@
         <v>44691</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62411,7 +62411,7 @@
         <v>45461</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62489,7 +62489,7 @@
         <v>45393</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62567,7 +62567,7 @@
         <v>44741</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62640,7 +62640,7 @@
         <v>44960</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62718,7 +62718,7 @@
         <v>44958</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>45729</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62869,7 +62869,7 @@
         <v>45782</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62947,7 +62947,7 @@
         <v>45821</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63025,7 +63025,7 @@
         <v>45821</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63103,7 +63103,7 @@
         <v>45796</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63176,7 +63176,7 @@
         <v>45841</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63254,7 +63254,7 @@
         <v>46125</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63332,7 +63332,7 @@
         <v>46125</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63410,7 +63410,7 @@
         <v>46129</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63488,7 +63488,7 @@
         <v>46135</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63561,7 +63561,7 @@
         <v>46135</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63634,7 +63634,7 @@
         <v>46135</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63707,7 +63707,7 @@
         <v>46174</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63780,7 +63780,7 @@
         <v>46176</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63853,7 +63853,7 @@
         <v>46252</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>

--- a/Översikt PAJALA.xlsx
+++ b/Översikt PAJALA.xlsx
@@ -601,7 +601,7 @@
         <v>45880</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>44874</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>45749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45345</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>44503</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>46197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45407</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>45845</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>44608</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>45306</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>46171</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>44588</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>44608</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45981</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>45405</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>46258</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>46260</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>44487</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>44874</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44608</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>44608</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>44893</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>44608</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>45964</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>45841</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>46211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>46291</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>45671</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44943</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44503</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45902</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>46029</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>46182</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>46182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>46212</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>46254</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>45469</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>45499</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>45959</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>45530</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>46052</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>45957</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44760</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>44755</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>46300</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44513</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45643</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>44608</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>45196</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>44945</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>45392</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>45973</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>44895</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>45530</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>45769</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>45476</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>46237</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>45215</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44771</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>45163</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>45897</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>45902</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>45755</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>45150</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44930</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>46107</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>44964</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>46034</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>46178</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>46182</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>46196</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>46204</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>46178</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>46216</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>46225</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>46274</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>46273</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>46275</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>46237</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>46258</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>46302</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>44496</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>45254</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>45216</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>44854</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>44854</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>45894</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>45894</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45497</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>45611</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>45585</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>45585</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>45791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>45356</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>45575</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>44608</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>45938</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>45820</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12048,7 +12048,7 @@
         <v>45832</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>45838</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>45875</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>45722</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>46125</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>46128</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>46035</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>45121</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         <v>46153</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>46188</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>46189</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>46189</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>46204</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>46196</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>46227</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>46276</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>46251</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>44579</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
         <v>45394</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>46080</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>44691</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44755</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>44691</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>44532</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>44755</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>44755</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>44755</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>44602</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44523</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>44691</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>44691</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>44691</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>44496</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>44700</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>44756</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>44622</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>44837</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>44879</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>44884</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44627</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>44642</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>44875</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>44552</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>44873</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>44873</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>44796</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>44521</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>44691</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44629</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>44518</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>44634</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>44592</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>44663</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>44860</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>44749</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>44834</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>44869</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44663</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>44663</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>44862</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>44627</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>44550</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44892</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>44627</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>44691</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>45467</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45434</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>45210</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45391</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>45334</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44743</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>45275</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>45215</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>45334</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>44892</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45270</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>45630</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>45613</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>45012</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>45309</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45592</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45307</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45450</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>45360</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>44960</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>45611</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>44574</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>45477</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>44968</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>45418</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45454</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>44568</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>44517</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>45371</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>45218</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>45770</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>45882</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>45204</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         <v>45201</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45463</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         <v>45884</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>45118</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>45611</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20351,7 +20351,7 @@
         <v>45169</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>44854</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>45247</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20580,7 +20580,7 @@
         <v>45278</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>45474</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>45463</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>45271</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>44894</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>45265</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
         <v>45671</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>45154</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>45573</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>45580</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>45297</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>44790</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>45682</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>44970</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>45477</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>45455</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>45314</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>45498</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21904,7 +21904,7 @@
         <v>44908</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>44944</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>44892</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>45491</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>45469</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>44837</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>45427</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>45894</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>45895</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>45898</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>45897</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>45898</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>44889</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>45385</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>45603</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>45902</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>44973</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>45624</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45601</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>45899</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>45227</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>45902</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>44884</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23618,7 +23618,7 @@
         <v>45033</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>45665</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>45427</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>45505</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>45906</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>45114</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>45905</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>44874</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>45621</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>45603</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>45523</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>45909</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24504,7 +24504,7 @@
         <v>45597</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>45475</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>45909</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>45236</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45611</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45454</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>45566</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>45780</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>45782</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>45558</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>44988</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>45914</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>45560</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>45002</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>45557</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>45678</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>45918</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>45918</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25838,7 +25838,7 @@
         <v>45447</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>45592</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>45592</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>45922</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>45919</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>45919</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>45919</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>45418</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>45006</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>45923</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>44959</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>45486</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>45923</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>45217</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45613</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45926</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27031,7 +27031,7 @@
         <v>45925</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>45481</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27177,7 +27177,7 @@
         <v>45589</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
         <v>45925</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>45630</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44568</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>45796</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>45794</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>45631</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>44641</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>45488</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>45586</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>45585</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>44552</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>45491</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>45058</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>45579</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>45579</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>45936</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>45934</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>45660</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>45660</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>44578</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>45936</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>45936</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44923</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>45936</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29017,7 +29017,7 @@
         <v>45407</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>45407</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>45936</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>45064</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>45801</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>45764</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>44755</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>45372</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44860</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>45177</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>44973</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>45938</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>44959</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>45807</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>45671</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30137,7 +30137,7 @@
         <v>44791</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>45870</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>45667</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>45558</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>45251</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>44988</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30580,7 +30580,7 @@
         <v>45002</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>45938</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30731,7 +30731,7 @@
         <v>45939</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30804,7 +30804,7 @@
         <v>45938</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>45938</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>45938</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31023,7 +31023,7 @@
         <v>45943</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31096,7 +31096,7 @@
         <v>45944</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>45399</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31242,7 +31242,7 @@
         <v>45407</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>45712</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45943</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>44691</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>44968</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>45736</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>45131</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>45820</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>45820</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>44874</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>45820</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>45623</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>45820</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>45821</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>45472</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>45630</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>45472</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>45583</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45177</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45583</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>45827</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>44615</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>44860</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>45523</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>45709</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>45583</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>45387</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33253,7 +33253,7 @@
         <v>45832</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33331,7 +33331,7 @@
         <v>45136</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>45944</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33477,7 +33477,7 @@
         <v>45631</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33550,7 +33550,7 @@
         <v>45964</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>45187</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33696,7 +33696,7 @@
         <v>45964</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>45838</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33847,7 +33847,7 @@
         <v>45630</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>45838</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33998,7 +33998,7 @@
         <v>44832</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34071,7 +34071,7 @@
         <v>45840</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34149,7 +34149,7 @@
         <v>45965</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34222,7 +34222,7 @@
         <v>45841</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>45968</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>45631</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>45210</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>45968</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34587,7 +34587,7 @@
         <v>45972</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34660,7 +34660,7 @@
         <v>45972</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34733,7 +34733,7 @@
         <v>45972</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34806,7 +34806,7 @@
         <v>45665</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>45970</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>45972</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35025,7 +35025,7 @@
         <v>45972</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>45972</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>44841</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35244,7 +35244,7 @@
         <v>45972</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35317,7 +35317,7 @@
         <v>45972</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35390,7 +35390,7 @@
         <v>45972</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>45972</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35536,7 +35536,7 @@
         <v>45971</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35614,7 +35614,7 @@
         <v>45972</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35687,7 +35687,7 @@
         <v>45972</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>45849</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35838,7 +35838,7 @@
         <v>45849</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>44778</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45736</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>45196</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>45592</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>45856</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>44756</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>45855</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36432,7 +36432,7 @@
         <v>45316</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45309</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         <v>45227</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>44504</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>45440</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36802,7 +36802,7 @@
         <v>45863</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>45868</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>45975</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>44861</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>45980</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37182,7 +37182,7 @@
         <v>45443</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37260,7 +37260,7 @@
         <v>45477</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>45482</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>45873</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>45873</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>45210</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>45238</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>45238</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>45162</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>45877</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>45475</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45880</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38068,7 +38068,7 @@
         <v>45877</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38141,7 +38141,7 @@
         <v>44824</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38214,7 +38214,7 @@
         <v>45880</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38287,7 +38287,7 @@
         <v>45981</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38360,7 +38360,7 @@
         <v>44834</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>45880</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>45258</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>45882</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>45882</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>45212</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>45981</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38881,7 +38881,7 @@
         <v>45981</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>45698</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>45616</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>45136</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>44916</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>45247</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
         <v>45265</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>46106</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45523</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>45523</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39611,7 +39611,7 @@
         <v>46108</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39684,7 +39684,7 @@
         <v>45180</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>46108</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>45988</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>46108</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45054</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40049,7 +40049,7 @@
         <v>45406</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40122,7 +40122,7 @@
         <v>46113</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>45599</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>45540</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>44910</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>45740</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40492,7 +40492,7 @@
         <v>44518</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>46125</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>45995</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>44522</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>46002</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40867,7 +40867,7 @@
         <v>46127</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>46128</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>46132</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41091,7 +41091,7 @@
         <v>46002</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41169,7 +41169,7 @@
         <v>46132</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41242,7 +41242,7 @@
         <v>45566</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41315,7 +41315,7 @@
         <v>44804</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41388,7 +41388,7 @@
         <v>44988</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41461,7 +41461,7 @@
         <v>46002</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>46002</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>46131</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41690,7 +41690,7 @@
         <v>46002</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>46002</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41836,7 +41836,7 @@
         <v>46133</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41909,7 +41909,7 @@
         <v>46133</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>44960</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42060,7 +42060,7 @@
         <v>44960</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>45586</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>45586</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>46133</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>46006</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42430,7 +42430,7 @@
         <v>46133</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
         <v>46006</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>46006</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42649,7 +42649,7 @@
         <v>46134</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42722,7 +42722,7 @@
         <v>46135</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42795,7 +42795,7 @@
         <v>46135</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>46136</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>46135</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>46135</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>46135</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>46135</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43233,7 +43233,7 @@
         <v>46136</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43306,7 +43306,7 @@
         <v>45216</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43379,7 +43379,7 @@
         <v>44958</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>46135</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>45862</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>46020</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43676,7 +43676,7 @@
         <v>46020</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>46021</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43822,7 +43822,7 @@
         <v>46021</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>46139</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>44547</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>46029</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>46030</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45152</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>46029</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44338,7 +44338,7 @@
         <v>46029</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>46029</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44494,7 +44494,7 @@
         <v>46031</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44567,7 +44567,7 @@
         <v>46031</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>46034</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>45031</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44786,7 +44786,7 @@
         <v>46038</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45602</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>44608</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>46048</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45088,7 +45088,7 @@
         <v>45475</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45910</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>45575</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>46049</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45012</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45607</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>46049</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>46052</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45682,7 +45682,7 @@
         <v>46058</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>46059</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>46059</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>46059</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>46059</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>46146</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>46063</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>46065</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>46064</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>46147</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46417,7 +46417,7 @@
         <v>46065</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>46072</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>46077</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>44755</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46709,7 +46709,7 @@
         <v>46078</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46782,7 +46782,7 @@
         <v>45989</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46855,7 +46855,7 @@
         <v>45952</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>46078</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>46083</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>46083</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47157,7 +47157,7 @@
         <v>46083</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47235,7 +47235,7 @@
         <v>46080</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47308,7 +47308,7 @@
         <v>46080</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47381,7 +47381,7 @@
         <v>46080</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47454,7 +47454,7 @@
         <v>46155</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47532,7 +47532,7 @@
         <v>46090</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47610,7 +47610,7 @@
         <v>44968</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47683,7 +47683,7 @@
         <v>46162</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
         <v>44968</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47829,7 +47829,7 @@
         <v>46162</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>46162</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>45443</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48048,7 +48048,7 @@
         <v>46161</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48121,7 +48121,7 @@
         <v>45878</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>45960</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48267,7 +48267,7 @@
         <v>45970</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48340,7 +48340,7 @@
         <v>45972</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48413,7 +48413,7 @@
         <v>45960</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>45736</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48559,7 +48559,7 @@
         <v>46173</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>46173</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48705,7 +48705,7 @@
         <v>46171</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>46170</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>46177</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48929,7 +48929,7 @@
         <v>46181</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>46181</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49080,7 +49080,7 @@
         <v>46181</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45970</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>46182</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>46181</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>46181</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49450,7 +49450,7 @@
         <v>46181</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49523,7 +49523,7 @@
         <v>46181</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49596,7 +49596,7 @@
         <v>46181</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>46183</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>46185</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49820,7 +49820,7 @@
         <v>46185</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49898,7 +49898,7 @@
         <v>46185</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49976,7 +49976,7 @@
         <v>46185</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50054,7 +50054,7 @@
         <v>46185</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>46185</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50210,7 +50210,7 @@
         <v>46185</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50288,7 +50288,7 @@
         <v>46185</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50366,7 +50366,7 @@
         <v>46190</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>46190</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         <v>46190</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50585,7 +50585,7 @@
         <v>46195</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50663,7 +50663,7 @@
         <v>46195</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50741,7 +50741,7 @@
         <v>46195</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50819,7 +50819,7 @@
         <v>46199</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>46199</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50965,7 +50965,7 @@
         <v>46199</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51043,7 +51043,7 @@
         <v>46198</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51121,7 +51121,7 @@
         <v>46203</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51199,7 +51199,7 @@
         <v>46204</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51277,7 +51277,7 @@
         <v>46204</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51355,7 +51355,7 @@
         <v>46167</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>45163</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>46209</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         <v>46206</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>46206</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51745,7 +51745,7 @@
         <v>46209</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51823,7 +51823,7 @@
         <v>46146</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51896,7 +51896,7 @@
         <v>46206</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51974,7 +51974,7 @@
         <v>46210</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>46178</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52130,7 +52130,7 @@
         <v>46210</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>46212</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52286,7 +52286,7 @@
         <v>46212</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         <v>46157</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52442,7 +52442,7 @@
         <v>46204</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52520,7 +52520,7 @@
         <v>45541</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52598,7 +52598,7 @@
         <v>45957</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52676,7 +52676,7 @@
         <v>45831</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
         <v>46214</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52827,7 +52827,7 @@
         <v>46212</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52905,7 +52905,7 @@
         <v>46212</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52983,7 +52983,7 @@
         <v>46148</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53061,7 +53061,7 @@
         <v>46212</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53139,7 +53139,7 @@
         <v>46157</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53217,7 +53217,7 @@
         <v>45884</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53295,7 +53295,7 @@
         <v>45548</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53368,7 +53368,7 @@
         <v>46265</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53441,7 +53441,7 @@
         <v>46265</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53514,7 +53514,7 @@
         <v>46266</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53587,7 +53587,7 @@
         <v>46223</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53660,7 +53660,7 @@
         <v>46223</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53733,7 +53733,7 @@
         <v>46265</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53806,7 +53806,7 @@
         <v>46266</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53879,7 +53879,7 @@
         <v>46223</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53952,7 +53952,7 @@
         <v>46223</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54025,7 +54025,7 @@
         <v>46265</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54098,7 +54098,7 @@
         <v>46223</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54171,7 +54171,7 @@
         <v>46225</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54249,7 +54249,7 @@
         <v>46225</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54327,7 +54327,7 @@
         <v>46225</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54405,7 +54405,7 @@
         <v>46267</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>46225</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54561,7 +54561,7 @@
         <v>46225</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54639,7 +54639,7 @@
         <v>46225</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54717,7 +54717,7 @@
         <v>46227</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54790,7 +54790,7 @@
         <v>46134</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54863,7 +54863,7 @@
         <v>46226</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         <v>46273</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55014,7 +55014,7 @@
         <v>46274</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55092,7 +55092,7 @@
         <v>46274</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>46274</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55238,7 +55238,7 @@
         <v>46273</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55311,7 +55311,7 @@
         <v>46274</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55384,7 +55384,7 @@
         <v>46198</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55457,7 +55457,7 @@
         <v>46231</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55530,7 +55530,7 @@
         <v>46273</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55603,7 +55603,7 @@
         <v>46276</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55676,7 +55676,7 @@
         <v>46275</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55754,7 +55754,7 @@
         <v>46280</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55832,7 +55832,7 @@
         <v>46279</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55905,7 +55905,7 @@
         <v>46234</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55978,7 +55978,7 @@
         <v>46280</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56051,7 +56051,7 @@
         <v>46280</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56129,7 +56129,7 @@
         <v>46237</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56202,7 +56202,7 @@
         <v>46280</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56280,7 +56280,7 @@
         <v>46280</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56358,7 +56358,7 @@
         <v>46280</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56431,7 +56431,7 @@
         <v>46237</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         <v>46234</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>46279</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56650,7 +56650,7 @@
         <v>46234</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56723,7 +56723,7 @@
         <v>46274</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56796,7 +56796,7 @@
         <v>46240</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56869,7 +56869,7 @@
         <v>46282</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56947,7 +56947,7 @@
         <v>46239</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57025,7 +57025,7 @@
         <v>46265</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57098,7 +57098,7 @@
         <v>46274</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57171,7 +57171,7 @@
         <v>46240</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57244,7 +57244,7 @@
         <v>46281</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57322,7 +57322,7 @@
         <v>46206</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57395,7 +57395,7 @@
         <v>46274</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57468,7 +57468,7 @@
         <v>46286</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57546,7 +57546,7 @@
         <v>46241</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57624,7 +57624,7 @@
         <v>46243</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57697,7 +57697,7 @@
         <v>46241</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57770,7 +57770,7 @@
         <v>45974</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57843,7 +57843,7 @@
         <v>45611</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57916,7 +57916,7 @@
         <v>45062</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57989,7 +57989,7 @@
         <v>46244</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         <v>45925</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58135,7 +58135,7 @@
         <v>46245</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58213,7 +58213,7 @@
         <v>46288</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58291,7 +58291,7 @@
         <v>45930</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58364,7 +58364,7 @@
         <v>46245</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58442,7 +58442,7 @@
         <v>46284</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58515,7 +58515,7 @@
         <v>46244</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>46245</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58666,7 +58666,7 @@
         <v>46247</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58744,7 +58744,7 @@
         <v>45707</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58817,7 +58817,7 @@
         <v>46246</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58890,7 +58890,7 @@
         <v>46246</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58963,7 +58963,7 @@
         <v>46246</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59036,7 +59036,7 @@
         <v>46246</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59109,7 +59109,7 @@
         <v>46146</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59182,7 +59182,7 @@
         <v>46246</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59255,7 +59255,7 @@
         <v>46289</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59333,7 +59333,7 @@
         <v>45777</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>46248</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59484,7 +59484,7 @@
         <v>46290</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59557,7 +59557,7 @@
         <v>46248</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59635,7 +59635,7 @@
         <v>46290</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59708,7 +59708,7 @@
         <v>46290</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59781,7 +59781,7 @@
         <v>46290</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59854,7 +59854,7 @@
         <v>46246</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59927,7 +59927,7 @@
         <v>46252</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60000,7 +60000,7 @@
         <v>46290</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>46251</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60151,7 +60151,7 @@
         <v>46252</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         <v>46252</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60302,7 +60302,7 @@
         <v>46251</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60380,7 +60380,7 @@
         <v>46253</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60458,7 +60458,7 @@
         <v>45370</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60531,7 +60531,7 @@
         <v>46258</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60609,7 +60609,7 @@
         <v>46258</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60687,7 +60687,7 @@
         <v>46258</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60765,7 +60765,7 @@
         <v>46254</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60843,7 +60843,7 @@
         <v>46254</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60921,7 +60921,7 @@
         <v>46258</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60999,7 +60999,7 @@
         <v>46258</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61077,7 +61077,7 @@
         <v>46251</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61150,7 +61150,7 @@
         <v>45968</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61223,7 +61223,7 @@
         <v>46298</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61296,7 +61296,7 @@
         <v>46251</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61374,7 +61374,7 @@
         <v>46258</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61452,7 +61452,7 @@
         <v>46258</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61530,7 +61530,7 @@
         <v>46301</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61603,7 +61603,7 @@
         <v>46132</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61676,7 +61676,7 @@
         <v>46301</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61749,7 +61749,7 @@
         <v>45356</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61822,7 +61822,7 @@
         <v>45356</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61895,7 +61895,7 @@
         <v>46303</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61968,7 +61968,7 @@
         <v>46261</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62046,7 +62046,7 @@
         <v>44579</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62119,7 +62119,7 @@
         <v>44691</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62192,7 +62192,7 @@
         <v>44578</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62265,7 +62265,7 @@
         <v>44578</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62338,7 +62338,7 @@
         <v>44691</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62411,7 +62411,7 @@
         <v>45461</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62489,7 +62489,7 @@
         <v>45393</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62567,7 +62567,7 @@
         <v>44741</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62640,7 +62640,7 @@
         <v>44960</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62718,7 +62718,7 @@
         <v>44958</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>45729</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62869,7 +62869,7 @@
         <v>45782</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62947,7 +62947,7 @@
         <v>45821</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63025,7 +63025,7 @@
         <v>45821</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63103,7 +63103,7 @@
         <v>45796</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63176,7 +63176,7 @@
         <v>45841</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63254,7 +63254,7 @@
         <v>46125</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63332,7 +63332,7 @@
         <v>46125</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63410,7 +63410,7 @@
         <v>46129</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63488,7 +63488,7 @@
         <v>46135</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63561,7 +63561,7 @@
         <v>46135</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63634,7 +63634,7 @@
         <v>46135</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63707,7 +63707,7 @@
         <v>46174</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63780,7 +63780,7 @@
         <v>46176</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63853,7 +63853,7 @@
         <v>46252</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>

--- a/Översikt PAJALA.xlsx
+++ b/Översikt PAJALA.xlsx
@@ -601,7 +601,7 @@
         <v>45880</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>44874</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>45749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45345</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>44503</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>46197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45407</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>45845</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>44608</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>45306</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>46171</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>44588</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>44608</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45981</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>45405</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>46258</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>46260</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>44487</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>44608</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44874</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>44608</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>44893</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>45964</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>46211</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>46291</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>45841</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>45671</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44943</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44503</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45902</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>46029</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>46182</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>46182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>46212</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>46254</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>46309</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45469</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>45499</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>45959</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>46052</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>45957</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>45530</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>44760</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>44755</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>46300</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>44513</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>45643</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>45392</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>44608</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>45476</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         <v>44945</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45973</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>44895</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45530</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>46237</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>45196</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>45769</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>45150</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44771</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>45163</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>45897</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         <v>44930</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45902</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>46034</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>46178</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>45755</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>46182</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>46196</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>45215</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>46107</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44964</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>46204</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>46178</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9432,7 +9432,7 @@
         <v>46216</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>46225</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>46273</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>46274</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>46275</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>46237</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>46258</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>46302</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>44496</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>44608</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>45356</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>45575</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>45585</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>45894</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>45894</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>46153</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>45938</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>45254</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>45611</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>45497</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         <v>45722</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>46035</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>45585</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>46188</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>46189</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>46189</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>46125</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>46128</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>46204</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>44854</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>44854</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>46178</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>45121</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>46196</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>46227</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>46276</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>45216</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>46251</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>45791</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>46307</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>45820</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45832</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>45838</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>45875</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>44579</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>45394</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>46080</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>44755</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>44691</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>44532</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>44691</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44755</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44755</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>44755</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44602</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>44691</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>44691</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>44691</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>44496</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>44700</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>44523</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>44756</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>44622</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>44879</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>44837</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>44884</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>44627</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44642</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>44875</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>44691</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>44629</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>44592</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44634</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>44663</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>44869</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>44627</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16684,7 +16684,7 @@
         <v>44873</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16757,7 +16757,7 @@
         <v>44873</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>44518</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>44834</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44663</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17049,7 +17049,7 @@
         <v>44550</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>44552</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>44796</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>44749</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>44663</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>44521</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>44860</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44862</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44627</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>44691</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45467</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45575</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44804</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45613</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>45275</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>44874</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45698</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>45454</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>45238</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45238</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>44504</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45611</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>44608</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>45523</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>45611</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>45217</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>44960</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>44960</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>45477</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45054</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>45665</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>44522</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>45540</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45573</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>45475</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44874</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>45566</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>44756</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>44892</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>44517</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>44910</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>45486</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>45169</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45187</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>45601</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>45201</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45592</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>45455</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45227</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45334</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>45180</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45477</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>45505</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45154</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>45678</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>45334</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>45583</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45227</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>44884</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45482</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45447</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45631</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45667</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45387</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>44894</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>44916</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45469</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45882</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>45764</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>44960</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>44547</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45660</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>45660</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45481</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>44568</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45215</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>46136</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45557</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>46134</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>45579</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>45579</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45177</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>45895</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>44973</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45894</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>46136</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>45897</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>45474</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>45477</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>45899</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45884</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>45898</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>45910</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>45898</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>45152</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45491</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45902</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>45902</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>45316</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24386,7 +24386,7 @@
         <v>45454</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>45434</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24532,7 +24532,7 @@
         <v>45905</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>45906</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>45909</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>45599</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>45603</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>45909</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>45862</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>45914</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>46147</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25214,7 +25214,7 @@
         <v>45918</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>46146</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>45919</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>45919</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>45918</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45923</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45923</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>45922</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>45919</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>45297</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>45925</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>45925</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>45926</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>44968</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>45936</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>45934</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45936</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>45936</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>44518</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>45936</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>45936</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>44578</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45938</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>45938</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>45938</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45498</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>45406</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27215,7 +27215,7 @@
         <v>45012</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>45671</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>45938</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>45938</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>44892</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>45870</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>45939</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>45943</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27809,7 +27809,7 @@
         <v>45943</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27882,7 +27882,7 @@
         <v>45944</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>44861</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>45624</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45177</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>45623</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>44755</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>46155</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>45616</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45118</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>45586</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45586</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45580</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>45944</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>45058</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>45560</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>44790</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>44968</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>45965</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>45964</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29279,7 +29279,7 @@
         <v>45964</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>45427</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>45630</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>45970</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         <v>45968</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>44968</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29717,7 +29717,7 @@
         <v>45971</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>45968</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29868,7 +29868,7 @@
         <v>45972</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>46162</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>45218</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30087,7 +30087,7 @@
         <v>45972</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45972</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30233,7 +30233,7 @@
         <v>45972</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>45972</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30379,7 +30379,7 @@
         <v>45972</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30452,7 +30452,7 @@
         <v>45972</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>45972</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30598,7 +30598,7 @@
         <v>45972</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30671,7 +30671,7 @@
         <v>45972</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>45972</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>45972</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30890,7 +30890,7 @@
         <v>46162</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
         <v>45975</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31036,7 +31036,7 @@
         <v>46162</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>46161</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31182,7 +31182,7 @@
         <v>45136</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>44988</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31328,7 +31328,7 @@
         <v>45592</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31401,7 +31401,7 @@
         <v>45592</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45981</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31547,7 +31547,7 @@
         <v>45960</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31620,7 +31620,7 @@
         <v>45981</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         <v>45981</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>45878</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>45980</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>45682</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>45265</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>45972</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>45247</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>44778</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>44755</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>44834</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>45736</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>45960</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32574,7 +32574,7 @@
         <v>45970</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32647,7 +32647,7 @@
         <v>45443</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32720,7 +32720,7 @@
         <v>45988</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>45740</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32866,7 +32866,7 @@
         <v>45995</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>45443</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33022,7 +33022,7 @@
         <v>45314</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33095,7 +33095,7 @@
         <v>46171</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>46170</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>46002</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>46002</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>46002</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>46002</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>46002</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>46002</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>46006</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33777,7 +33777,7 @@
         <v>46006</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>46006</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>45589</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>46173</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>45031</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34142,7 +34142,7 @@
         <v>46173</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45270</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>46020</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>45631</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>46021</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>46021</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>46020</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>46029</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>46029</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>46029</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>46029</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>46031</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>46031</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>46030</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>46034</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>46181</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>46181</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>46181</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>45970</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>46177</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>46038</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45210</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>44837</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>44552</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>46181</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>46181</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>46181</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>44908</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45440</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36284,7 +36284,7 @@
         <v>46049</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>46048</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44889</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36508,7 +36508,7 @@
         <v>46049</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>45597</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>46182</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36737,7 +36737,7 @@
         <v>45611</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36810,7 +36810,7 @@
         <v>46181</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36888,7 +36888,7 @@
         <v>45523</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>46181</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37039,7 +37039,7 @@
         <v>46052</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45064</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>46183</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37258,7 +37258,7 @@
         <v>46059</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37331,7 +37331,7 @@
         <v>46059</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37404,7 +37404,7 @@
         <v>46185</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37482,7 +37482,7 @@
         <v>46059</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37555,7 +37555,7 @@
         <v>46058</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>46059</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>44841</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>46063</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>46064</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>46065</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>46065</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
         <v>45271</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>46185</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>45630</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38290,7 +38290,7 @@
         <v>46185</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38368,7 +38368,7 @@
         <v>46072</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>46185</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38519,7 +38519,7 @@
         <v>46078</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38592,7 +38592,7 @@
         <v>46185</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38670,7 +38670,7 @@
         <v>46077</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>46185</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>46078</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38894,7 +38894,7 @@
         <v>46185</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38972,7 +38972,7 @@
         <v>46185</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39050,7 +39050,7 @@
         <v>45952</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39123,7 +39123,7 @@
         <v>45989</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>46080</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39269,7 +39269,7 @@
         <v>46080</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>46080</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39415,7 +39415,7 @@
         <v>45463</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>46190</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39566,7 +39566,7 @@
         <v>46083</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>46083</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39722,7 +39722,7 @@
         <v>46083</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39800,7 +39800,7 @@
         <v>46090</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39878,7 +39878,7 @@
         <v>46190</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39951,7 +39951,7 @@
         <v>45391</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40024,7 +40024,7 @@
         <v>46190</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>44970</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44860</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>45131</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>46195</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40394,7 +40394,7 @@
         <v>46195</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40472,7 +40472,7 @@
         <v>46106</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>46195</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>46108</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40696,7 +40696,7 @@
         <v>45558</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>44958</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40842,7 +40842,7 @@
         <v>46108</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40915,7 +40915,7 @@
         <v>46108</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>46198</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>45418</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>46199</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41212,7 +41212,7 @@
         <v>46113</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41285,7 +41285,7 @@
         <v>45012</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41358,7 +41358,7 @@
         <v>44973</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41431,7 +41431,7 @@
         <v>45450</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>44691</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>46199</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41660,7 +41660,7 @@
         <v>46125</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>46127</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41811,7 +41811,7 @@
         <v>46128</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41884,7 +41884,7 @@
         <v>46199</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41957,7 +41957,7 @@
         <v>46132</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>46133</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>46133</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42176,7 +42176,7 @@
         <v>46132</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42249,7 +42249,7 @@
         <v>46204</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>46131</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>46133</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>46133</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42546,7 +42546,7 @@
         <v>46135</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42619,7 +42619,7 @@
         <v>46203</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>46135</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>46135</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>46135</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>46135</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>46135</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>46135</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>46204</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45360</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>45665</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>46146</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>45307</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43505,7 +43505,7 @@
         <v>46139</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45247</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43651,7 +43651,7 @@
         <v>46206</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>44854</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43807,7 +43807,7 @@
         <v>46206</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43885,7 +43885,7 @@
         <v>46206</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43963,7 +43963,7 @@
         <v>45613</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>44944</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45163</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>46167</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45114</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44338,7 +44338,7 @@
         <v>45586</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44411,7 +44411,7 @@
         <v>46210</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45212</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>46210</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>46209</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>46209</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>46212</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>45204</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>46212</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>46212</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>46212</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>45385</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>45541</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>46214</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45405,7 +45405,7 @@
         <v>46157</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45483,7 +45483,7 @@
         <v>45884</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>46204</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45639,7 +45639,7 @@
         <v>46157</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>44641</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45831</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>46148</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>45957</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46024,7 +46024,7 @@
         <v>45407</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>45407</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46170,7 +46170,7 @@
         <v>44615</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46243,7 +46243,7 @@
         <v>44568</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>45548</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>46265</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46462,7 +46462,7 @@
         <v>45196</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>46223</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>46223</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>46223</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>46223</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>46223</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>46225</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>46225</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>46225</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47134,7 +47134,7 @@
         <v>46225</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47212,7 +47212,7 @@
         <v>46225</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47290,7 +47290,7 @@
         <v>46225</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47368,7 +47368,7 @@
         <v>46226</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47441,7 +47441,7 @@
         <v>45488</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47519,7 +47519,7 @@
         <v>45523</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>45523</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>46273</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47743,7 +47743,7 @@
         <v>46227</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47816,7 +47816,7 @@
         <v>45372</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47894,7 +47894,7 @@
         <v>46273</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47967,7 +47967,7 @@
         <v>46273</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48040,7 +48040,7 @@
         <v>46231</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48113,7 +48113,7 @@
         <v>46274</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>46274</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48264,7 +48264,7 @@
         <v>46274</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>45210</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>46198</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48483,7 +48483,7 @@
         <v>46274</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48556,7 +48556,7 @@
         <v>46275</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48634,7 +48634,7 @@
         <v>46279</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48707,7 +48707,7 @@
         <v>46279</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48780,7 +48780,7 @@
         <v>46237</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48853,7 +48853,7 @@
         <v>46234</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>45607</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         <v>46237</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49072,7 +49072,7 @@
         <v>45278</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49145,7 +49145,7 @@
         <v>46234</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49218,7 +49218,7 @@
         <v>46234</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49291,7 +49291,7 @@
         <v>45602</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49364,7 +49364,7 @@
         <v>46276</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49437,7 +49437,7 @@
         <v>45265</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49510,7 +49510,7 @@
         <v>46274</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49583,7 +49583,7 @@
         <v>45216</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49656,7 +49656,7 @@
         <v>46281</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>46274</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49807,7 +49807,7 @@
         <v>46280</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49880,7 +49880,7 @@
         <v>46274</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>46280</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>45258</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>46280</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50177,7 +50177,7 @@
         <v>45407</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50250,7 +50250,7 @@
         <v>44574</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50323,7 +50323,7 @@
         <v>46280</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50401,7 +50401,7 @@
         <v>46280</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50479,7 +50479,7 @@
         <v>46280</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         <v>45603</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50635,7 +50635,7 @@
         <v>44923</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>46240</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>46241</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50854,7 +50854,7 @@
         <v>46240</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50927,7 +50927,7 @@
         <v>45210</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51000,7 +51000,7 @@
         <v>45709</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51073,7 +51073,7 @@
         <v>46239</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51151,7 +51151,7 @@
         <v>45770</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>46206</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>46282</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51375,7 +51375,7 @@
         <v>44988</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51448,7 +51448,7 @@
         <v>46284</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51521,7 +51521,7 @@
         <v>45925</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51594,7 +51594,7 @@
         <v>45371</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51672,7 +51672,7 @@
         <v>45974</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51745,7 +51745,7 @@
         <v>45427</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51818,7 +51818,7 @@
         <v>46243</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>45671</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51964,7 +51964,7 @@
         <v>46244</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45611</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52110,7 +52110,7 @@
         <v>45062</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52183,7 +52183,7 @@
         <v>45631</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52256,7 +52256,7 @@
         <v>45136</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52329,7 +52329,7 @@
         <v>45475</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>45930</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>46241</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52553,7 +52553,7 @@
         <v>46286</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52631,7 +52631,7 @@
         <v>46244</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>44988</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52777,7 +52777,7 @@
         <v>46246</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>46245</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>46246</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         <v>46246</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         <v>46245</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53152,7 +53152,7 @@
         <v>46245</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53230,7 +53230,7 @@
         <v>46246</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53303,7 +53303,7 @@
         <v>46246</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>46289</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53454,7 +53454,7 @@
         <v>45309</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53532,7 +53532,7 @@
         <v>45309</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53610,7 +53610,7 @@
         <v>45630</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53683,7 +53683,7 @@
         <v>44832</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53756,7 +53756,7 @@
         <v>45583</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53834,7 +53834,7 @@
         <v>44959</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53907,7 +53907,7 @@
         <v>44743</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53980,7 +53980,7 @@
         <v>45777</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         <v>46248</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54131,7 +54131,7 @@
         <v>46146</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54204,7 +54204,7 @@
         <v>46247</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54282,7 +54282,7 @@
         <v>44892</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54355,7 +54355,7 @@
         <v>44959</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54433,7 +54433,7 @@
         <v>45463</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>45491</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>45621</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54657,7 +54657,7 @@
         <v>46246</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54730,7 +54730,7 @@
         <v>46248</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54808,7 +54808,7 @@
         <v>45418</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54881,7 +54881,7 @@
         <v>45585</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54954,7 +54954,7 @@
         <v>45707</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55027,7 +55027,7 @@
         <v>46252</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55100,7 +55100,7 @@
         <v>46252</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55178,7 +55178,7 @@
         <v>44968</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55251,7 +55251,7 @@
         <v>45251</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55324,7 +55324,7 @@
         <v>46290</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>46290</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55470,7 +55470,7 @@
         <v>46290</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55543,7 +55543,7 @@
         <v>45370</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55616,7 +55616,7 @@
         <v>46251</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55694,7 +55694,7 @@
         <v>45583</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55772,7 +55772,7 @@
         <v>46252</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55845,7 +55845,7 @@
         <v>46251</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55923,7 +55923,7 @@
         <v>45566</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55996,7 +55996,7 @@
         <v>44824</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56069,7 +56069,7 @@
         <v>46290</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56142,7 +56142,7 @@
         <v>46290</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56215,7 +56215,7 @@
         <v>46251</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56293,7 +56293,7 @@
         <v>45736</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>45630</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56439,7 +56439,7 @@
         <v>45162</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56512,7 +56512,7 @@
         <v>45592</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>45968</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56658,7 +56658,7 @@
         <v>46254</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56736,7 +56736,7 @@
         <v>46253</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56814,7 +56814,7 @@
         <v>46254</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56892,7 +56892,7 @@
         <v>46251</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56965,7 +56965,7 @@
         <v>46258</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57043,7 +57043,7 @@
         <v>46258</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57121,7 +57121,7 @@
         <v>45033</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57194,7 +57194,7 @@
         <v>46258</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57272,7 +57272,7 @@
         <v>46258</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57350,7 +57350,7 @@
         <v>46301</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57423,7 +57423,7 @@
         <v>46258</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57501,7 +57501,7 @@
         <v>45236</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57574,7 +57574,7 @@
         <v>45558</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57647,7 +57647,7 @@
         <v>46298</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57720,7 +57720,7 @@
         <v>45782</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57793,7 +57793,7 @@
         <v>45780</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57866,7 +57866,7 @@
         <v>46258</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>46258</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58022,7 +58022,7 @@
         <v>46301</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58095,7 +58095,7 @@
         <v>45356</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58168,7 +58168,7 @@
         <v>45006</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58246,7 +58246,7 @@
         <v>46303</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58319,7 +58319,7 @@
         <v>45002</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58397,7 +58397,7 @@
         <v>45356</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58470,7 +58470,7 @@
         <v>46261</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58548,7 +58548,7 @@
         <v>46306</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58621,7 +58621,7 @@
         <v>45794</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58694,7 +58694,7 @@
         <v>45796</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58772,7 +58772,7 @@
         <v>46212</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58850,7 +58850,7 @@
         <v>46265</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58923,7 +58923,7 @@
         <v>46265</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58996,7 +58996,7 @@
         <v>46309</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59069,7 +59069,7 @@
         <v>46309</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59142,7 +59142,7 @@
         <v>45801</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59215,7 +59215,7 @@
         <v>46308</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         <v>46279</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59361,7 +59361,7 @@
         <v>46266</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59434,7 +59434,7 @@
         <v>46309</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59512,7 +59512,7 @@
         <v>46309</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59585,7 +59585,7 @@
         <v>46309</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59658,7 +59658,7 @@
         <v>46309</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59731,7 +59731,7 @@
         <v>46267</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59809,7 +59809,7 @@
         <v>46309</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59882,7 +59882,7 @@
         <v>44860</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59955,7 +59955,7 @@
         <v>46266</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60028,7 +60028,7 @@
         <v>45807</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60106,7 +60106,7 @@
         <v>46132</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60179,7 +60179,7 @@
         <v>46309</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60252,7 +60252,7 @@
         <v>46265</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60325,7 +60325,7 @@
         <v>46134</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60398,7 +60398,7 @@
         <v>46265</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60471,7 +60471,7 @@
         <v>46309</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60549,7 +60549,7 @@
         <v>44791</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60622,7 +60622,7 @@
         <v>45712</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60695,7 +60695,7 @@
         <v>45002</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60773,7 +60773,7 @@
         <v>45399</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60846,7 +60846,7 @@
         <v>46309</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60919,7 +60919,7 @@
         <v>45736</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60992,7 +60992,7 @@
         <v>45821</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61070,7 +61070,7 @@
         <v>45820</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61143,7 +61143,7 @@
         <v>45820</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61216,7 +61216,7 @@
         <v>45820</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61294,7 +61294,7 @@
         <v>46311</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61367,7 +61367,7 @@
         <v>45472</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61440,7 +61440,7 @@
         <v>45820</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61513,7 +61513,7 @@
         <v>45472</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61586,7 +61586,7 @@
         <v>45827</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61664,7 +61664,7 @@
         <v>46311</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61737,7 +61737,7 @@
         <v>46311</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61810,7 +61810,7 @@
         <v>45832</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61888,7 +61888,7 @@
         <v>45838</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61966,7 +61966,7 @@
         <v>45838</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62044,7 +62044,7 @@
         <v>45840</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62122,7 +62122,7 @@
         <v>45841</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62195,7 +62195,7 @@
         <v>45849</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62273,7 +62273,7 @@
         <v>45849</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62351,7 +62351,7 @@
         <v>45855</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62429,7 +62429,7 @@
         <v>45856</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62502,7 +62502,7 @@
         <v>45863</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62575,7 +62575,7 @@
         <v>45868</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62653,7 +62653,7 @@
         <v>45873</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62726,7 +62726,7 @@
         <v>45873</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62799,7 +62799,7 @@
         <v>45877</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62872,7 +62872,7 @@
         <v>45877</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62945,7 +62945,7 @@
         <v>45880</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63018,7 +63018,7 @@
         <v>45475</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63091,7 +63091,7 @@
         <v>45880</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63164,7 +63164,7 @@
         <v>45880</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63242,7 +63242,7 @@
         <v>45882</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63320,7 +63320,7 @@
         <v>45882</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63398,7 +63398,7 @@
         <v>45461</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63476,7 +63476,7 @@
         <v>45393</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63554,7 +63554,7 @@
         <v>44579</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63627,7 +63627,7 @@
         <v>44741</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63700,7 +63700,7 @@
         <v>44960</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>44691</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63851,7 +63851,7 @@
         <v>44958</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63924,7 +63924,7 @@
         <v>44578</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63997,7 +63997,7 @@
         <v>44578</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64070,7 +64070,7 @@
         <v>44691</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64143,7 +64143,7 @@
         <v>45729</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64221,7 +64221,7 @@
         <v>45782</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64299,7 +64299,7 @@
         <v>45821</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64377,7 +64377,7 @@
         <v>45821</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64455,7 +64455,7 @@
         <v>45796</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64528,7 +64528,7 @@
         <v>45841</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64606,7 +64606,7 @@
         <v>46125</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64684,7 +64684,7 @@
         <v>46125</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64762,7 +64762,7 @@
         <v>46129</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64840,7 +64840,7 @@
         <v>46135</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64913,7 +64913,7 @@
         <v>46135</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64986,7 +64986,7 @@
         <v>46135</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65059,7 +65059,7 @@
         <v>46174</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65132,7 +65132,7 @@
         <v>46176</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65205,7 +65205,7 @@
         <v>46252</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>

--- a/Översikt PAJALA.xlsx
+++ b/Översikt PAJALA.xlsx
@@ -601,7 +601,7 @@
         <v>45880</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>44874</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>45749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45345</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>44503</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>46197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45407</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>45845</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>44608</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>45306</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>46171</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>44588</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>44608</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45981</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>45405</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>46258</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>46260</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>44487</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>44608</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44874</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>44608</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>44893</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>45964</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>46211</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>46291</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>45841</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>45671</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>44943</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44503</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45902</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>46029</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>46182</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>46182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>46212</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>46254</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>46309</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45469</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>45499</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>45959</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>46052</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>45957</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>45530</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>44760</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>44755</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>46300</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>44513</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>45643</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>45392</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>44608</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>45476</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         <v>44945</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45973</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>44895</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45530</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>46237</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>45196</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>45769</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>45150</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44771</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>45163</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>45897</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         <v>44930</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45902</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>46034</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>46178</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>45755</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>46182</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>46196</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>45215</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>46107</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44964</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>46204</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>46178</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9432,7 +9432,7 @@
         <v>46216</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>46225</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>46273</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>46274</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>46275</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>46237</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>46258</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>46302</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>44496</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>44608</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>45356</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>45575</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>45585</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>45894</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>45894</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>46153</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>45938</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>45254</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>45611</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>45497</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         <v>45722</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>46035</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>45585</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>46188</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>46189</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>46189</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>46125</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>46128</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>46204</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>44854</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>44854</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>46178</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>45121</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>46196</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>46227</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>46276</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>45216</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>46251</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>45791</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>46307</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>45820</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45832</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>45838</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>45875</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>44579</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>45394</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>46080</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>44755</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>44691</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>44532</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>44691</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44755</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44755</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>44755</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44602</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>44691</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>44691</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>44691</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>44496</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>44700</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>44523</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>44756</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>44622</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>44879</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>44837</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>44884</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>44627</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44642</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>44875</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>44691</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>44629</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>44592</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44634</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>44663</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>44869</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>44627</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16684,7 +16684,7 @@
         <v>44873</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16757,7 +16757,7 @@
         <v>44873</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>44518</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>44834</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>44663</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17049,7 +17049,7 @@
         <v>44550</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>44552</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>44796</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>44749</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>44663</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>44521</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>44860</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44862</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44627</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>44691</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45467</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45575</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44804</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45613</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>45275</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>44874</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45698</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>45454</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>45238</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45238</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>44504</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45611</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>44608</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>45523</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>45611</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>45217</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>44960</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>44960</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>45477</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45054</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>45665</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>44522</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>45540</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45573</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>45475</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44874</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>45566</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>44756</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>44892</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>44517</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>44910</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>45486</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>45169</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45187</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>45601</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>45201</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45592</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>45455</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45227</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45334</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>45180</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45477</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>45505</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45154</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>45678</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>45334</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>45583</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45227</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>44884</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45482</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45447</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45631</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45667</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45387</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>44894</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>44916</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45469</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45882</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>45764</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>44960</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>44547</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45660</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>45660</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45481</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>44568</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45215</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>46136</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45557</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>46134</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>45579</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>45579</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45177</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>45895</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>44973</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45894</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>46136</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>45897</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>45474</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>45477</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>45899</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45884</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>45898</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>45910</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>45898</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>45152</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45491</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45902</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>45902</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>45316</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24386,7 +24386,7 @@
         <v>45454</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>45434</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24532,7 +24532,7 @@
         <v>45905</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>45906</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>45909</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>45599</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>45603</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>45909</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>45862</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>45914</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>46147</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25214,7 +25214,7 @@
         <v>45918</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>46146</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>45919</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>45919</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>45918</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45923</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45923</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>45922</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>45919</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>45297</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>45925</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>45925</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>45926</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>44968</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>45936</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>45934</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45936</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>45936</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>44518</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>45936</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>45936</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>44578</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45938</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>45938</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>45938</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45498</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>45406</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27215,7 +27215,7 @@
         <v>45012</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>45671</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>45938</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>45938</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>44892</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>45870</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>45939</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>45943</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27809,7 +27809,7 @@
         <v>45943</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27882,7 +27882,7 @@
         <v>45944</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>44861</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>45624</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45177</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>45623</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>44755</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>46155</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>45616</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45118</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>45586</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45586</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45580</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>45944</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>45058</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>45560</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>44790</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>44968</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>45965</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>45964</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29279,7 +29279,7 @@
         <v>45964</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>45427</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>45630</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>45970</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         <v>45968</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>44968</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29717,7 +29717,7 @@
         <v>45971</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>45968</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29868,7 +29868,7 @@
         <v>45972</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>46162</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>45218</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30087,7 +30087,7 @@
         <v>45972</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45972</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30233,7 +30233,7 @@
         <v>45972</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>45972</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30379,7 +30379,7 @@
         <v>45972</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30452,7 +30452,7 @@
         <v>45972</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>45972</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30598,7 +30598,7 @@
         <v>45972</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30671,7 +30671,7 @@
         <v>45972</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>45972</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>45972</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30890,7 +30890,7 @@
         <v>46162</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
         <v>45975</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31036,7 +31036,7 @@
         <v>46162</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>46161</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31182,7 +31182,7 @@
         <v>45136</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>44988</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31328,7 +31328,7 @@
         <v>45592</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31401,7 +31401,7 @@
         <v>45592</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45981</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31547,7 +31547,7 @@
         <v>45960</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31620,7 +31620,7 @@
         <v>45981</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         <v>45981</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>45878</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>45980</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>45682</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>45265</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>45972</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>45247</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>44778</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>44755</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>44834</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>45736</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>45960</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32574,7 +32574,7 @@
         <v>45970</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32647,7 +32647,7 @@
         <v>45443</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32720,7 +32720,7 @@
         <v>45988</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>45740</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32866,7 +32866,7 @@
         <v>45995</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>45443</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33022,7 +33022,7 @@
         <v>45314</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33095,7 +33095,7 @@
         <v>46171</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>46170</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>46002</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>46002</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>46002</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>46002</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>46002</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>46002</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>46006</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33777,7 +33777,7 @@
         <v>46006</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>46006</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>45589</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>46173</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>45031</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34142,7 +34142,7 @@
         <v>46173</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45270</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>46020</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>45631</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>46021</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>46021</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>46020</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>46029</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>46029</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>46029</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>46029</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>46031</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>46031</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>46030</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>46034</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>46181</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>46181</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>46181</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>45970</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>46177</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>46038</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45210</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>44837</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>44552</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>46181</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>46181</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>46181</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>44908</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45440</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36284,7 +36284,7 @@
         <v>46049</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>46048</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44889</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36508,7 +36508,7 @@
         <v>46049</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>45597</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>46182</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36737,7 +36737,7 @@
         <v>45611</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36810,7 +36810,7 @@
         <v>46181</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36888,7 +36888,7 @@
         <v>45523</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>46181</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37039,7 +37039,7 @@
         <v>46052</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45064</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>46183</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37258,7 +37258,7 @@
         <v>46059</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37331,7 +37331,7 @@
         <v>46059</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37404,7 +37404,7 @@
         <v>46185</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37482,7 +37482,7 @@
         <v>46059</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37555,7 +37555,7 @@
         <v>46058</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>46059</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>44841</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>46063</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>46064</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>46065</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>46065</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
         <v>45271</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>46185</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>45630</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38290,7 +38290,7 @@
         <v>46185</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38368,7 +38368,7 @@
         <v>46072</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>46185</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38519,7 +38519,7 @@
         <v>46078</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38592,7 +38592,7 @@
         <v>46185</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38670,7 +38670,7 @@
         <v>46077</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>46185</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>46078</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38894,7 +38894,7 @@
         <v>46185</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38972,7 +38972,7 @@
         <v>46185</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39050,7 +39050,7 @@
         <v>45952</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39123,7 +39123,7 @@
         <v>45989</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>46080</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39269,7 +39269,7 @@
         <v>46080</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>46080</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39415,7 +39415,7 @@
         <v>45463</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>46190</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39566,7 +39566,7 @@
         <v>46083</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>46083</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39722,7 +39722,7 @@
         <v>46083</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39800,7 +39800,7 @@
         <v>46090</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39878,7 +39878,7 @@
         <v>46190</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39951,7 +39951,7 @@
         <v>45391</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40024,7 +40024,7 @@
         <v>46190</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>44970</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>44860</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>45131</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>46195</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40394,7 +40394,7 @@
         <v>46195</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40472,7 +40472,7 @@
         <v>46106</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>46195</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>46108</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40696,7 +40696,7 @@
         <v>45558</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>44958</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40842,7 +40842,7 @@
         <v>46108</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40915,7 +40915,7 @@
         <v>46108</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>46198</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>45418</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>46199</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41212,7 +41212,7 @@
         <v>46113</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41285,7 +41285,7 @@
         <v>45012</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41358,7 +41358,7 @@
         <v>44973</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41431,7 +41431,7 @@
         <v>45450</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>44691</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>46199</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41660,7 +41660,7 @@
         <v>46125</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>46127</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41811,7 +41811,7 @@
         <v>46128</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41884,7 +41884,7 @@
         <v>46199</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41957,7 +41957,7 @@
         <v>46132</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>46133</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>46133</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42176,7 +42176,7 @@
         <v>46132</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42249,7 +42249,7 @@
         <v>46204</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>46131</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>46133</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>46133</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42546,7 +42546,7 @@
         <v>46135</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42619,7 +42619,7 @@
         <v>46203</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>46135</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>46135</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>46135</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>46135</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>46135</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>46135</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>46204</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45360</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>45665</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>46146</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>45307</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43505,7 +43505,7 @@
         <v>46139</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45247</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43651,7 +43651,7 @@
         <v>46206</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>44854</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43807,7 +43807,7 @@
         <v>46206</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43885,7 +43885,7 @@
         <v>46206</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43963,7 +43963,7 @@
         <v>45613</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>44944</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45163</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>46167</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45114</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44338,7 +44338,7 @@
         <v>45586</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44411,7 +44411,7 @@
         <v>46210</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45212</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>46210</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>46209</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>46209</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>46212</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>45204</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>46212</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>46212</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>46212</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>45385</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>45541</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>46214</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45405,7 +45405,7 @@
         <v>46157</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45483,7 +45483,7 @@
         <v>45884</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>46204</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45639,7 +45639,7 @@
         <v>46157</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>44641</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45831</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>46148</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>45957</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46024,7 +46024,7 @@
         <v>45407</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>45407</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46170,7 +46170,7 @@
         <v>44615</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46243,7 +46243,7 @@
         <v>44568</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>45548</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>46265</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46462,7 +46462,7 @@
         <v>45196</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>46223</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>46223</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>46223</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>46223</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>46223</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>46225</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>46225</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>46225</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47134,7 +47134,7 @@
         <v>46225</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47212,7 +47212,7 @@
         <v>46225</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47290,7 +47290,7 @@
         <v>46225</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47368,7 +47368,7 @@
         <v>46226</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47441,7 +47441,7 @@
         <v>45488</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47519,7 +47519,7 @@
         <v>45523</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>45523</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>46273</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47743,7 +47743,7 @@
         <v>46227</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47816,7 +47816,7 @@
         <v>45372</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47894,7 +47894,7 @@
         <v>46273</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47967,7 +47967,7 @@
         <v>46273</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48040,7 +48040,7 @@
         <v>46231</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48113,7 +48113,7 @@
         <v>46274</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>46274</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48264,7 +48264,7 @@
         <v>46274</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>45210</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>46198</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48483,7 +48483,7 @@
         <v>46274</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48556,7 +48556,7 @@
         <v>46275</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48634,7 +48634,7 @@
         <v>46279</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48707,7 +48707,7 @@
         <v>46279</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48780,7 +48780,7 @@
         <v>46237</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48853,7 +48853,7 @@
         <v>46234</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>45607</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         <v>46237</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49072,7 +49072,7 @@
         <v>45278</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49145,7 +49145,7 @@
         <v>46234</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49218,7 +49218,7 @@
         <v>46234</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49291,7 +49291,7 @@
         <v>45602</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49364,7 +49364,7 @@
         <v>46276</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49437,7 +49437,7 @@
         <v>45265</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49510,7 +49510,7 @@
         <v>46274</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49583,7 +49583,7 @@
         <v>45216</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49656,7 +49656,7 @@
         <v>46281</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>46274</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49807,7 +49807,7 @@
         <v>46280</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49880,7 +49880,7 @@
         <v>46274</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>46280</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>45258</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>46280</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50177,7 +50177,7 @@
         <v>45407</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50250,7 +50250,7 @@
         <v>44574</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50323,7 +50323,7 @@
         <v>46280</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50401,7 +50401,7 @@
         <v>46280</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50479,7 +50479,7 @@
         <v>46280</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         <v>45603</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50635,7 +50635,7 @@
         <v>44923</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>46240</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>46241</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50854,7 +50854,7 @@
         <v>46240</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50927,7 +50927,7 @@
         <v>45210</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51000,7 +51000,7 @@
         <v>45709</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51073,7 +51073,7 @@
         <v>46239</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51151,7 +51151,7 @@
         <v>45770</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>46206</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>46282</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51375,7 +51375,7 @@
         <v>44988</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51448,7 +51448,7 @@
         <v>46284</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51521,7 +51521,7 @@
         <v>45925</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51594,7 +51594,7 @@
         <v>45371</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51672,7 +51672,7 @@
         <v>45974</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51745,7 +51745,7 @@
         <v>45427</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51818,7 +51818,7 @@
         <v>46243</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>45671</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51964,7 +51964,7 @@
         <v>46244</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45611</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52110,7 +52110,7 @@
         <v>45062</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52183,7 +52183,7 @@
         <v>45631</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52256,7 +52256,7 @@
         <v>45136</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52329,7 +52329,7 @@
         <v>45475</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>45930</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>46241</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52553,7 +52553,7 @@
         <v>46286</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52631,7 +52631,7 @@
         <v>46244</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>44988</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52777,7 +52777,7 @@
         <v>46246</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>46245</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>46246</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         <v>46246</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         <v>46245</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53152,7 +53152,7 @@
         <v>46245</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53230,7 +53230,7 @@
         <v>46246</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53303,7 +53303,7 @@
         <v>46246</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>46289</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53454,7 +53454,7 @@
         <v>45309</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53532,7 +53532,7 @@
         <v>45309</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53610,7 +53610,7 @@
         <v>45630</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53683,7 +53683,7 @@
         <v>44832</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53756,7 +53756,7 @@
         <v>45583</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53834,7 +53834,7 @@
         <v>44959</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53907,7 +53907,7 @@
         <v>44743</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53980,7 +53980,7 @@
         <v>45777</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         <v>46248</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54131,7 +54131,7 @@
         <v>46146</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54204,7 +54204,7 @@
         <v>46247</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54282,7 +54282,7 @@
         <v>44892</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54355,7 +54355,7 @@
         <v>44959</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54433,7 +54433,7 @@
         <v>45463</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>45491</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>45621</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54657,7 +54657,7 @@
         <v>46246</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54730,7 +54730,7 @@
         <v>46248</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54808,7 +54808,7 @@
         <v>45418</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54881,7 +54881,7 @@
         <v>45585</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54954,7 +54954,7 @@
         <v>45707</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55027,7 +55027,7 @@
         <v>46252</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55100,7 +55100,7 @@
         <v>46252</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55178,7 +55178,7 @@
         <v>44968</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55251,7 +55251,7 @@
         <v>45251</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55324,7 +55324,7 @@
         <v>46290</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>46290</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55470,7 +55470,7 @@
         <v>46290</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55543,7 +55543,7 @@
         <v>45370</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55616,7 +55616,7 @@
         <v>46251</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55694,7 +55694,7 @@
         <v>45583</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55772,7 +55772,7 @@
         <v>46252</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55845,7 +55845,7 @@
         <v>46251</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55923,7 +55923,7 @@
         <v>45566</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55996,7 +55996,7 @@
         <v>44824</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56069,7 +56069,7 @@
         <v>46290</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56142,7 +56142,7 @@
         <v>46290</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56215,7 +56215,7 @@
         <v>46251</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56293,7 +56293,7 @@
         <v>45736</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>45630</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56439,7 +56439,7 @@
         <v>45162</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56512,7 +56512,7 @@
         <v>45592</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>45968</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56658,7 +56658,7 @@
         <v>46254</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56736,7 +56736,7 @@
         <v>46253</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56814,7 +56814,7 @@
         <v>46254</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56892,7 +56892,7 @@
         <v>46251</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56965,7 +56965,7 @@
         <v>46258</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57043,7 +57043,7 @@
         <v>46258</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57121,7 +57121,7 @@
         <v>45033</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57194,7 +57194,7 @@
         <v>46258</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57272,7 +57272,7 @@
         <v>46258</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57350,7 +57350,7 @@
         <v>46301</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57423,7 +57423,7 @@
         <v>46258</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57501,7 +57501,7 @@
         <v>45236</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57574,7 +57574,7 @@
         <v>45558</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57647,7 +57647,7 @@
         <v>46298</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57720,7 +57720,7 @@
         <v>45782</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57793,7 +57793,7 @@
         <v>45780</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57866,7 +57866,7 @@
         <v>46258</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>46258</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58022,7 +58022,7 @@
         <v>46301</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58095,7 +58095,7 @@
         <v>45356</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58168,7 +58168,7 @@
         <v>45006</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58246,7 +58246,7 @@
         <v>46303</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58319,7 +58319,7 @@
         <v>45002</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58397,7 +58397,7 @@
         <v>45356</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58470,7 +58470,7 @@
         <v>46261</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58548,7 +58548,7 @@
         <v>46306</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58621,7 +58621,7 @@
         <v>45794</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58694,7 +58694,7 @@
         <v>45796</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58772,7 +58772,7 @@
         <v>46212</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58850,7 +58850,7 @@
         <v>46265</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58923,7 +58923,7 @@
         <v>46265</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58996,7 +58996,7 @@
         <v>46309</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59069,7 +59069,7 @@
         <v>46309</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59142,7 +59142,7 @@
         <v>45801</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59215,7 +59215,7 @@
         <v>46308</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         <v>46279</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59361,7 +59361,7 @@
         <v>46266</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59434,7 +59434,7 @@
         <v>46309</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59512,7 +59512,7 @@
         <v>46309</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59585,7 +59585,7 @@
         <v>46309</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59658,7 +59658,7 @@
         <v>46309</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59731,7 +59731,7 @@
         <v>46267</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59809,7 +59809,7 @@
         <v>46309</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59882,7 +59882,7 @@
         <v>44860</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59955,7 +59955,7 @@
         <v>46266</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60028,7 +60028,7 @@
         <v>45807</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60106,7 +60106,7 @@
         <v>46132</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60179,7 +60179,7 @@
         <v>46309</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60252,7 +60252,7 @@
         <v>46265</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60325,7 +60325,7 @@
         <v>46134</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60398,7 +60398,7 @@
         <v>46265</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60471,7 +60471,7 @@
         <v>46309</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60549,7 +60549,7 @@
         <v>44791</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60622,7 +60622,7 @@
         <v>45712</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60695,7 +60695,7 @@
         <v>45002</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60773,7 +60773,7 @@
         <v>45399</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60846,7 +60846,7 @@
         <v>46309</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60919,7 +60919,7 @@
         <v>45736</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60992,7 +60992,7 @@
         <v>45821</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61070,7 +61070,7 @@
         <v>45820</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61143,7 +61143,7 @@
         <v>45820</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61216,7 +61216,7 @@
         <v>45820</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61294,7 +61294,7 @@
         <v>46311</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61367,7 +61367,7 @@
         <v>45472</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61440,7 +61440,7 @@
         <v>45820</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61513,7 +61513,7 @@
         <v>45472</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61586,7 +61586,7 @@
         <v>45827</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61664,7 +61664,7 @@
         <v>46311</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61737,7 +61737,7 @@
         <v>46311</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61810,7 +61810,7 @@
         <v>45832</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61888,7 +61888,7 @@
         <v>45838</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61966,7 +61966,7 @@
         <v>45838</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62044,7 +62044,7 @@
         <v>45840</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62122,7 +62122,7 @@
         <v>45841</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62195,7 +62195,7 @@
         <v>45849</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62273,7 +62273,7 @@
         <v>45849</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62351,7 +62351,7 @@
         <v>45855</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62429,7 +62429,7 @@
         <v>45856</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62502,7 +62502,7 @@
         <v>45863</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62575,7 +62575,7 @@
         <v>45868</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62653,7 +62653,7 @@
         <v>45873</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62726,7 +62726,7 @@
         <v>45873</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62799,7 +62799,7 @@
         <v>45877</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62872,7 +62872,7 @@
         <v>45877</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62945,7 +62945,7 @@
         <v>45880</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63018,7 +63018,7 @@
         <v>45475</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63091,7 +63091,7 @@
         <v>45880</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63164,7 +63164,7 @@
         <v>45880</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63242,7 +63242,7 @@
         <v>45882</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63320,7 +63320,7 @@
         <v>45882</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63398,7 +63398,7 @@
         <v>45461</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63476,7 +63476,7 @@
         <v>45393</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63554,7 +63554,7 @@
         <v>44579</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63627,7 +63627,7 @@
         <v>44741</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63700,7 +63700,7 @@
         <v>44960</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>44691</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63851,7 +63851,7 @@
         <v>44958</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63924,7 +63924,7 @@
         <v>44578</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63997,7 +63997,7 @@
         <v>44578</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64070,7 +64070,7 @@
         <v>44691</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64143,7 +64143,7 @@
         <v>45729</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64221,7 +64221,7 @@
         <v>45782</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64299,7 +64299,7 @@
         <v>45821</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64377,7 +64377,7 @@
         <v>45821</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64455,7 +64455,7 @@
         <v>45796</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64528,7 +64528,7 @@
         <v>45841</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64606,7 +64606,7 @@
         <v>46125</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64684,7 +64684,7 @@
         <v>46125</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64762,7 +64762,7 @@
         <v>46129</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64840,7 +64840,7 @@
         <v>46135</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64913,7 +64913,7 @@
         <v>46135</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64986,7 +64986,7 @@
         <v>46135</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65059,7 +65059,7 @@
         <v>46174</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65132,7 +65132,7 @@
         <v>46176</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65205,7 +65205,7 @@
         <v>46252</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
